--- a/2 FINANCE/PREVISIONS/2026 1028 Modèle Pop Tables - Budget sur 36 mois, plan financier, prix et marges.xlsx
+++ b/2 FINANCE/PREVISIONS/2026 1028 Modèle Pop Tables - Budget sur 36 mois, plan financier, prix et marges.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\PREVISIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47501460-8397-4BCC-93DF-52AAF23A4E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9484D665-FFFB-470F-8705-E8648B22E82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="3" xr2:uid="{09426CC5-4BCC-48B7-8854-C5C8E2CE30D1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{09426CC5-4BCC-48B7-8854-C5C8E2CE30D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="475">
   <si>
     <t>Rubrique</t>
   </si>
@@ -1159,15 +1159,9 @@
     <t>Ville 2 (France)</t>
   </si>
   <si>
-    <t>Ville 3 (étranger)</t>
-  </si>
-  <si>
     <t>Étranger</t>
   </si>
   <si>
-    <t>Ville 4 (France)</t>
-  </si>
-  <si>
     <t>Ville 5 (étranger)</t>
   </si>
   <si>
@@ -1487,6 +1481,18 @@
   </si>
   <si>
     <t>Revu le 28/10/2026 (soir) par le responsable Finance : nouvelles villes actives dès novembre ; 40 privatisations par ville et par an dès l'année 2 ; coordinateurs (1 par événement hebdomadaire) et commerciaux (1 par ville active, dès l'année 3) calculés à partir de l'activité ; un manager en année 3 ; locaux et logiciels par poste payé ; prix et coûts revus dans « Prix et marges ». Décisions D-05, D-06, D-08, D-14, D-15, D-19 intégrées ; campagne de lancement (10 000 €), protection juridique et assurance (2 % du CA) et budget des ventes. Toutes les autres valeurs restent des hypothèses (H) : voir la fiche des données manquantes du 28/10/2026.</t>
+  </si>
+  <si>
+    <t>france</t>
+  </si>
+  <si>
+    <t>etranger</t>
+  </si>
+  <si>
+    <t>Ville 3 (france)</t>
+  </si>
+  <si>
+    <t>Ville 4 (Etranger)</t>
   </si>
 </sst>
 </file>
@@ -2234,12 +2240,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13" x14ac:dyDescent="0.25">
@@ -2263,7 +2269,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="50" x14ac:dyDescent="0.25">
@@ -2271,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25" x14ac:dyDescent="0.25">
@@ -2335,7 +2341,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="25" x14ac:dyDescent="0.25">
@@ -2478,10 +2484,10 @@
         <v>117</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -2507,7 +2513,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>83</v>
@@ -3003,10 +3009,10 @@
         <v>117</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -3183,7 +3189,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>51</v>
@@ -3204,10 +3210,10 @@
         <v>117</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -4854,7 +4860,7 @@
         <v>275</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -4985,7 +4991,7 @@
         <v>82</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -5563,7 +5569,7 @@
         <v>82</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -5729,7 +5735,7 @@
     </row>
     <row r="14" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B14" s="13">
         <f t="shared" si="1"/>
@@ -5855,12 +5861,12 @@
         <v>82</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B15" s="13">
         <f t="shared" si="1"/>
@@ -5991,7 +5997,7 @@
     </row>
     <row r="16" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B16" s="13">
         <f>SUM(E16:P16)</f>
@@ -6141,12 +6147,12 @@
         <v>117</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B17" s="13">
         <f>SUM(E17:P17)</f>
@@ -6296,7 +6302,7 @@
         <v>117</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -6563,7 +6569,7 @@
     </row>
     <row r="20" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B20" s="13">
         <f>MAX(E20:P20)</f>
@@ -6725,12 +6731,12 @@
         <v>117</v>
       </c>
       <c r="AP20" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B21" s="13">
         <f>MAX(E21:P21)</f>
@@ -6892,12 +6898,12 @@
         <v>117</v>
       </c>
       <c r="AP21" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B22" s="13">
         <f>MAX(E22:P22)</f>
@@ -7059,7 +7065,7 @@
         <v>117</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -8801,7 +8807,7 @@
         <v>117</v>
       </c>
       <c r="AP34" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AQ34" s="55"/>
     </row>
@@ -8970,7 +8976,7 @@
         <v>117</v>
       </c>
       <c r="AP35" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AQ35" s="55"/>
     </row>
@@ -9516,7 +9522,7 @@
         <v>117</v>
       </c>
       <c r="AP39" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AQ39" s="57">
         <f>TVA!$C$30</f>
@@ -9687,7 +9693,7 @@
         <v>117</v>
       </c>
       <c r="AP40" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AQ40" s="57">
         <f>TVA!$C$31</f>
@@ -11409,7 +11415,7 @@
         <v>117</v>
       </c>
       <c r="AP52" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AQ52" s="57">
         <v>0.1</v>
@@ -14857,8 +14863,7 @@
         <v>336</v>
       </c>
       <c r="B78" s="16">
-        <f>SUM(E78:P78)</f>
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="C78" s="16">
         <f>SUM(Q78:AB78)</f>
@@ -14869,7 +14874,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="14">
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="F78" s="14">
         <v>0</v>
@@ -14989,7 +14994,7 @@
       </c>
       <c r="B79" s="16">
         <f>SUM(E79:P79)</f>
-        <v>-8551.1785714285943</v>
+        <v>54448.821428571413</v>
       </c>
       <c r="C79" s="16">
         <f>SUM(Q79:AB79)</f>
@@ -15001,7 +15006,7 @@
       </c>
       <c r="E79" s="15">
         <f t="shared" ref="E79:AN79" si="36">E59-E64+E75+E77+E78</f>
-        <v>-17763</v>
+        <v>45237</v>
       </c>
       <c r="F79" s="15">
         <f t="shared" si="36"/>
@@ -15153,159 +15158,159 @@
       </c>
       <c r="B80" s="16">
         <f>P80</f>
-        <v>-8551.1785714285943</v>
+        <v>54448.821428571413</v>
       </c>
       <c r="C80" s="16">
         <f>AB80</f>
-        <v>433353.49647619051</v>
+        <v>496353.49647619051</v>
       </c>
       <c r="D80" s="16">
         <f>AN80</f>
-        <v>808460.35847619059</v>
+        <v>871460.35847619059</v>
       </c>
       <c r="E80" s="16">
         <f>E79</f>
-        <v>-17763</v>
+        <v>45237</v>
       </c>
       <c r="F80" s="16">
         <f t="shared" ref="F80:AN80" si="37">E80+F79</f>
-        <v>-11514.000000000002</v>
+        <v>51486</v>
       </c>
       <c r="G80" s="16">
         <f t="shared" si="37"/>
-        <v>-3016.6428571428605</v>
+        <v>59983.357142857145</v>
       </c>
       <c r="H80" s="16">
         <f t="shared" si="37"/>
-        <v>-13995.642857142862</v>
+        <v>49004.357142857145</v>
       </c>
       <c r="I80" s="16">
         <f t="shared" si="37"/>
-        <v>-52928.892857142862</v>
+        <v>10071.107142857145</v>
       </c>
       <c r="J80" s="16">
         <f t="shared" si="37"/>
-        <v>-38639.17857142858</v>
+        <v>24360.821428571428</v>
       </c>
       <c r="K80" s="16">
         <f t="shared" si="37"/>
-        <v>-36919.821428571442</v>
+        <v>26080.178571428565</v>
       </c>
       <c r="L80" s="16">
         <f t="shared" si="37"/>
-        <v>-34340.714285714304</v>
+        <v>28659.285714285703</v>
       </c>
       <c r="M80" s="16">
         <f t="shared" si="37"/>
-        <v>-44263.357142857159</v>
+        <v>18736.642857142848</v>
       </c>
       <c r="N80" s="16">
         <f t="shared" si="37"/>
-        <v>-35674.357142857159</v>
+        <v>27325.642857142848</v>
       </c>
       <c r="O80" s="16">
         <f t="shared" si="37"/>
-        <v>-40242.642857142877</v>
+        <v>22757.35714285713</v>
       </c>
       <c r="P80" s="16">
         <f t="shared" si="37"/>
-        <v>-8551.1785714285943</v>
+        <v>54448.821428571413</v>
       </c>
       <c r="Q80" s="16">
         <f t="shared" si="37"/>
-        <v>27445.629666666646</v>
+        <v>90445.629666666646</v>
       </c>
       <c r="R80" s="16">
         <f t="shared" si="37"/>
-        <v>69142.437904761886</v>
+        <v>132142.43790476187</v>
       </c>
       <c r="S80" s="16">
         <f t="shared" si="37"/>
-        <v>109803.04376190473</v>
+        <v>172803.04376190473</v>
       </c>
       <c r="T80" s="16">
         <f t="shared" si="37"/>
-        <v>146472.34009523806</v>
+        <v>209472.34009523806</v>
       </c>
       <c r="U80" s="16">
         <f t="shared" si="37"/>
-        <v>183141.63642857139</v>
+        <v>246141.63642857139</v>
       </c>
       <c r="V80" s="16">
         <f t="shared" si="37"/>
-        <v>219810.93276190473</v>
+        <v>282810.93276190473</v>
       </c>
       <c r="W80" s="16">
         <f t="shared" si="37"/>
-        <v>256480.22909523806</v>
+        <v>319480.22909523803</v>
       </c>
       <c r="X80" s="16">
         <f t="shared" si="37"/>
-        <v>293149.52542857139</v>
+        <v>356149.52542857139</v>
       </c>
       <c r="Y80" s="16">
         <f t="shared" si="37"/>
-        <v>282818.82176190475</v>
+        <v>345818.82176190475</v>
       </c>
       <c r="Z80" s="16">
         <f t="shared" si="37"/>
-        <v>342104.01095238095</v>
+        <v>405104.01095238095</v>
       </c>
       <c r="AA80" s="16">
         <f t="shared" si="37"/>
-        <v>364684.20014285715</v>
+        <v>427684.20014285715</v>
       </c>
       <c r="AB80" s="16">
         <f t="shared" si="37"/>
-        <v>433353.49647619051</v>
+        <v>496353.49647619051</v>
       </c>
       <c r="AC80" s="16">
         <f t="shared" si="37"/>
-        <v>460328.93438095244</v>
+        <v>523328.93438095244</v>
       </c>
       <c r="AD80" s="16">
         <f t="shared" si="37"/>
-        <v>494454.19371428579</v>
+        <v>557454.19371428574</v>
       </c>
       <c r="AE80" s="16">
         <f t="shared" si="37"/>
-        <v>527179.45304761908</v>
+        <v>590179.45304761908</v>
       </c>
       <c r="AF80" s="16">
         <f t="shared" si="37"/>
-        <v>559904.71238095243</v>
+        <v>622904.71238095243</v>
       </c>
       <c r="AG80" s="16">
         <f t="shared" si="37"/>
-        <v>592629.97171428578</v>
+        <v>655629.97171428578</v>
       </c>
       <c r="AH80" s="16">
         <f t="shared" si="37"/>
-        <v>625355.23104761913</v>
+        <v>688355.23104761913</v>
       </c>
       <c r="AI80" s="16">
         <f t="shared" si="37"/>
-        <v>658080.49038095248</v>
+        <v>721080.49038095248</v>
       </c>
       <c r="AJ80" s="16">
         <f t="shared" si="37"/>
-        <v>690805.74971428583</v>
+        <v>753805.74971428583</v>
       </c>
       <c r="AK80" s="16">
         <f t="shared" si="37"/>
-        <v>629531.00904761918</v>
+        <v>692531.00904761918</v>
       </c>
       <c r="AL80" s="16">
         <f t="shared" si="37"/>
-        <v>741258.05409523821</v>
+        <v>804258.05409523821</v>
       </c>
       <c r="AM80" s="16">
         <f t="shared" si="37"/>
-        <v>775735.09914285725</v>
+        <v>838735.09914285725</v>
       </c>
       <c r="AN80" s="16">
         <f t="shared" si="37"/>
-        <v>808460.35847619059</v>
+        <v>871460.35847619059</v>
       </c>
     </row>
     <row r="82" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -15436,46 +15441,46 @@
     </row>
     <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B90" s="71">
         <v>40</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B91" s="71">
         <v>300</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B92" s="71">
         <v>80</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B93" s="71">
         <v>50</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="95" spans="1:43" ht="26" x14ac:dyDescent="0.25">
@@ -15520,72 +15525,72 @@
         <v>46692</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>363</v>
+        <v>473</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>364</v>
+        <v>471</v>
       </c>
       <c r="C98" s="52">
         <f>EDATE($B$3,12)</f>
         <v>46692</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>365</v>
+        <v>474</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>360</v>
+        <v>472</v>
       </c>
       <c r="C99" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C100" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C101" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -15607,7 +15612,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.3">
@@ -15861,7 +15866,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B20" s="1">
         <v>33</v>
@@ -16021,7 +16026,7 @@
         <v>249</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C30" s="41">
         <v>0.2</v>
@@ -16038,7 +16043,7 @@
         <v>250</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C31" s="41">
         <v>0.2</v>
@@ -16055,7 +16060,7 @@
         <v>110</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C32" s="41">
         <v>0.2</v>
@@ -16069,10 +16074,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C33" s="41">
         <v>0</v>
@@ -16089,7 +16094,7 @@
         <v>253</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C34" s="41">
         <v>0.2</v>
@@ -16106,7 +16111,7 @@
         <v>112</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C35" s="41">
         <v>0</v>
@@ -16123,7 +16128,7 @@
         <v>113</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C36" s="41">
         <v>0.1</v>
@@ -16140,7 +16145,7 @@
         <v>114</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C37" s="41">
         <v>0</v>
@@ -16154,10 +16159,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C38" s="41">
         <v>0.2</v>
@@ -16171,7 +16176,7 @@
     </row>
     <row r="40" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="60" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B40"/>
       <c r="C40"/>
@@ -16525,12 +16530,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -17254,7 +17259,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="59" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -17268,7 +17273,7 @@
     </row>
     <row r="2" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -17344,10 +17349,10 @@
     </row>
     <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C7" s="66">
         <f>'Budget 36 mois'!B7</f>
@@ -17362,7 +17367,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -17371,10 +17376,10 @@
     </row>
     <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C8" s="66">
         <f>'Budget 36 mois'!B11</f>
@@ -17389,7 +17394,7 @@
         <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -17398,10 +17403,10 @@
     </row>
     <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B9" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C9" s="66">
         <f>'Budget 36 mois'!B8</f>
@@ -17423,10 +17428,10 @@
     </row>
     <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C10" s="66">
         <f>'Budget 36 mois'!B9</f>
@@ -17448,10 +17453,10 @@
     </row>
     <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C11" s="66">
         <f>'Budget 36 mois'!B10</f>
@@ -17473,10 +17478,10 @@
     </row>
     <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C12" s="66">
         <f>'Budget 36 mois'!B12</f>
@@ -17491,7 +17496,7 @@
         <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
@@ -17503,7 +17508,7 @@
         <v>107</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C13" s="69">
         <f>'Budget 36 mois'!B13</f>
@@ -17564,7 +17569,7 @@
     </row>
     <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
@@ -17629,7 +17634,7 @@
     </row>
     <row r="19" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -17647,7 +17652,7 @@
         <v>643836.88800000015</v>
       </c>
       <c r="F19" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -17681,7 +17686,7 @@
     </row>
     <row r="21" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B21" t="s">
         <v>51</v>
@@ -17699,7 +17704,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -17708,7 +17713,7 @@
     </row>
     <row r="22" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B22" t="s">
         <v>51</v>
@@ -17726,7 +17731,7 @@
         <v>29210.000000000004</v>
       </c>
       <c r="F22" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -17735,7 +17740,7 @@
     </row>
     <row r="23" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
@@ -17785,7 +17790,7 @@
     </row>
     <row r="25" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
@@ -17803,7 +17808,7 @@
         <v>76559.999999999971</v>
       </c>
       <c r="F25" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
@@ -17862,7 +17867,7 @@
     </row>
     <row r="28" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="37" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
@@ -17876,7 +17881,7 @@
     </row>
     <row r="29" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
@@ -17901,7 +17906,7 @@
     </row>
     <row r="30" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B30" t="s">
         <v>132</v>
@@ -17969,7 +17974,7 @@
         <v>212.59935743716258</v>
       </c>
       <c r="F32" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
@@ -17990,7 +17995,7 @@
     </row>
     <row r="34" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="37" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="37"/>
@@ -18004,7 +18009,7 @@
     </row>
     <row r="35" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="38" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B35" s="38" t="s">
         <v>132</v>
@@ -18023,14 +18028,14 @@
     </row>
     <row r="36" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="38" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B36" s="38" t="s">
         <v>132</v>
       </c>
       <c r="C36" s="36">
         <f>MIN('Budget 36 mois'!E80:AN80)</f>
-        <v>-52928.892857142862</v>
+        <v>10071.107142857145</v>
       </c>
       <c r="D36" s="64"/>
       <c r="E36" s="64"/>
@@ -18042,7 +18047,7 @@
     </row>
     <row r="37" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B37"/>
       <c r="C37" s="70">
@@ -18059,22 +18064,22 @@
     </row>
     <row r="38" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B38" t="s">
         <v>132</v>
       </c>
       <c r="C38" s="64">
         <f>'Budget 36 mois'!P80</f>
-        <v>-8551.1785714285943</v>
+        <v>54448.821428571413</v>
       </c>
       <c r="D38" s="64">
         <f>'Budget 36 mois'!AB80</f>
-        <v>433353.49647619051</v>
+        <v>496353.49647619051</v>
       </c>
       <c r="E38" s="64">
         <f>'Budget 36 mois'!AN80</f>
-        <v>808460.35847619059</v>
+        <v>871460.35847619059</v>
       </c>
       <c r="F38"/>
       <c r="G38"/>
@@ -18084,7 +18089,7 @@
     </row>
     <row r="39" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
@@ -18121,7 +18126,7 @@
     </row>
     <row r="41" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="60" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
@@ -18380,12 +18385,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="59" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -18401,24 +18406,24 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C5" s="74">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C6" s="74">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -18426,16 +18431,16 @@
         <v>26</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C7" s="62" t="s">
         <v>139</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F7" s="62" t="s">
         <v>140</v>
@@ -18512,7 +18517,7 @@
         <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -18545,12 +18550,12 @@
         <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="34" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B11" s="34">
         <v>1</v>
@@ -18577,7 +18582,7 @@
         <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -18605,7 +18610,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="60" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/2 FINANCE/PREVISIONS/2026 1028 Modèle Pop Tables - Budget sur 36 mois, plan financier, prix et marges.xlsx
+++ b/2 FINANCE/PREVISIONS/2026 1028 Modèle Pop Tables - Budget sur 36 mois, plan financier, prix et marges.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\PREVISIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9484D665-FFFB-470F-8705-E8648B22E82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032AA5BA-CFB8-4D80-9C66-00DDF09E1545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{09426CC5-4BCC-48B7-8854-C5C8E2CE30D1}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="474">
   <si>
     <t>Rubrique</t>
   </si>
@@ -322,12 +322,6 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>5 PRODUIT/Fou d'un soir le pricing.md (@Fréd, 27/10/2026), prix des soirées et grille de privatisation (prix TTC tout compris)</t>
-  </si>
-  <si>
-    <t>5 PRODUIT/Fou d'un soir le pricing.md (@Fréd, 27/10/2026), forfait de privatisation chef confirmé ; H : forfait supposé TTC comme les prix de l'offre A</t>
-  </si>
-  <si>
     <t>Taux mixte (le pricing le signale « à vérifier avec la finance ») : 10 % sur la restauration, 20 % sur les boissons alcoolisées (règle fiscale à confirmer par un expert-comptable) ; H : boissons alcoolisées environ 20 % du prix</t>
   </si>
   <si>
@@ -913,9 +907,6 @@
     <t>Privatisations de salle (B2C et B2B, chef confirmé)</t>
   </si>
   <si>
-    <t>Soirées « place à l'unité » des villes 3, 5 et 6. Prix, coûts et TVA supposés identiques à Paris (H)</t>
-  </si>
-  <si>
     <t>Pilote Premier soir (inclus ligne 8)</t>
   </si>
   <si>
@@ -1078,12 +1069,6 @@
     <t>D-04 : places à l'unité payées à la réservation. H : vente au drop, le mois qui précède la soirée ; encaissement TTC. Privatisations payées le mois de la soirée (acompte et solde, H). Mois 36 : pré-vente du mois suivant non comptée (prudence)</t>
   </si>
   <si>
-    <t>Apport des associés</t>
-  </si>
-  <si>
-    <t>Modèle Financement : 7 000 € (7 associés × 1 000 €), statut « Envisagé », aucune pièce</t>
-  </si>
-  <si>
     <t>Flux de trésorerie du mois</t>
   </si>
   <si>
@@ -1123,9 +1108,6 @@
     <t>Coût d'ouverture d'une ville à l'étranger (€)</t>
   </si>
   <si>
-    <t>H : idem, plus conseils juridiques et fiscaux locaux (Juridique, D-15)</t>
-  </si>
-  <si>
     <t>Places offertes aux prescripteurs par soirée « place à l'unité »</t>
   </si>
   <si>
@@ -1138,9 +1120,6 @@
     <t>H : fixé par le responsable Finance le 28/10/2026</t>
   </si>
   <si>
-    <t>Ville (D-15)</t>
-  </si>
-  <si>
     <t>Pays</t>
   </si>
   <si>
@@ -1255,9 +1234,6 @@
     <t>Privatisations de salle</t>
   </si>
   <si>
-    <t>H en attendant les Ventes (D-16)</t>
-  </si>
-  <si>
     <t>Coûts directs (y compris déplacements de production)</t>
   </si>
   <si>
@@ -1303,9 +1279,6 @@
     <t>Besoin de financement : point bas du flux cumulé (hors apport, TVA et pré-vente)</t>
   </si>
   <si>
-    <t>Trésorerie : point bas sur 36 mois (apport de 7 000 €, TVA et pré-vente compris, avant levée)</t>
-  </si>
-  <si>
     <t>Mois du point bas</t>
   </si>
   <si>
@@ -1318,9 +1291,6 @@
     <t>Le dimensionnement de la levée (contingence, trésorerie de sécurité) se trouve dans 2 FINANCE/FINANCEMENT, note pour décision du 28/10/2026 (soir). Le financement se suit dans le modèle Financement.</t>
   </si>
   <si>
-    <t>Décision D-05 de la Direction du 28/10/2026 (« Jauge — validé suivant fichier finance ») : 40 / 35 / 30 / 20 couverts. Relevé de décisions du 28/10 (soir)</t>
-  </si>
-  <si>
     <t>Direction</t>
   </si>
   <si>
@@ -1363,33 +1333,12 @@
     <t>dont privatisations hors Paris, à l'étranger</t>
   </si>
   <si>
-    <t>Privatisations (ligne 12) des villes 2 et 4 : 40 par ville et par an (B86). Pas de frais de déplacement de production (décision du 28/10/2026)</t>
-  </si>
-  <si>
-    <t>Privatisations (ligne 12) des villes 3, 5 et 6 : idem. Pas de frais de déplacement de production ; prix, coûts et TVA identiques à Paris (H)</t>
-  </si>
-  <si>
-    <t>D-16 : année 1 = 7 privatisations (budget du 27/10). À partir de l'année 2 : 40 par ville active et par an (paramètre B86), soit villes actives × 40 / 12 par mois</t>
-  </si>
-  <si>
-    <t>D-15 pour l'année ; ville active dès le premier mois de l'année (novembre) ; ville à choisir par la Direction sur proposition du Marketing et des Ventes</t>
-  </si>
-  <si>
-    <t>Décision D-15 : Paris en année 1 ; + 1 ville en France et + 1 à l'étranger en année 2 ; + 1 en France et + 2 à l'étranger en année 3. Les nouvelles villes sont actives dès le début de l'année (novembre) ; villes non nommées</t>
-  </si>
-  <si>
     <t>D-15 : 1 soirée « place à l'unité » par mois et par ville, pas de soirée en août (H). Les trois offres tournent dans chaque ville (H) : 1/1/1 par mois en année 2, 2/2/2 en année 3. Année 1 : calendrier du budget du 27/10, pilotes compris</t>
   </si>
   <si>
-    <t>Repérage, déplacements, communication locale, recrutement des extras, conseils locaux : coût par ville en France (B82) ou à l'étranger (B83), réparti sur les 3 mois qui précèdent la première soirée (dates C90:C94). Calculé automatiquement</t>
-  </si>
-  <si>
     <t>Villes actives (dès le début d'année)</t>
   </si>
   <si>
-    <t>D-15 ; nouvelles villes ouvertes en novembre</t>
-  </si>
-  <si>
     <t>Événements par semaine gérés par un coordinateur</t>
   </si>
   <si>
@@ -1468,31 +1417,79 @@
     <t>Socle mensuel (B92) + effectif total payé (ligne 22) × licences par poste (B93)</t>
   </si>
   <si>
-    <t>Soirées « place à l'unité » des villes 2 et 4 ; seules ces soirées portent des frais de déplacement (ligne 29)</t>
-  </si>
-  <si>
     <t>Pop Tables · poste par poste. Le coût mensuel est repris dans « Budget 36 mois », lignes 33 à 36, à partir du premier mois payé ; effectifs mois par mois aux lignes 20 à 22.</t>
   </si>
   <si>
-    <t>Pour changer une ouverture de ville : modifier la date en C97:C101 (la ligne 52 se recalcule) et les lignes 7 à 10, 14 et 15 (valeurs saisies). Les totaux et le plan à 3 ans se recalculent.</t>
-  </si>
-  <si>
-    <t>Pop Tables · Pôle Finance · Version du 28/10/2026 (soir), selon les décisions D-02 à D-20, revue par le responsable Finance. Remplace le modèle du 27/10 (rangé dans 2 FINANCE/OLD).</t>
-  </si>
-  <si>
-    <t>Revu le 28/10/2026 (soir) par le responsable Finance : nouvelles villes actives dès novembre ; 40 privatisations par ville et par an dès l'année 2 ; coordinateurs (1 par événement hebdomadaire) et commerciaux (1 par ville active, dès l'année 3) calculés à partir de l'activité ; un manager en année 3 ; locaux et logiciels par poste payé ; prix et coûts revus dans « Prix et marges ». Décisions D-05, D-06, D-08, D-14, D-15, D-19 intégrées ; campagne de lancement (10 000 €), protection juridique et assurance (2 % du CA) et budget des ventes. Toutes les autres valeurs restent des hypothèses (H) : voir la fiche des données manquantes du 28/10/2026.</t>
-  </si>
-  <si>
-    <t>france</t>
-  </si>
-  <si>
-    <t>etranger</t>
-  </si>
-  <si>
-    <t>Ville 3 (france)</t>
-  </si>
-  <si>
-    <t>Ville 4 (Etranger)</t>
+    <t>Décisions D-15, D-21 et D-25 : Paris en année 1 ; 2 nouvelles villes en France actives dès novembre 2027 (3 villes) ; 3 villes à l'étranger actives dès novembre 2028 (6 villes). Villes non nommées</t>
+  </si>
+  <si>
+    <t>D-16 et D-21 : année 1 = 7 privatisations (budget du 27/10). À partir de l'année 2 : 40 par ville active et par an (paramètre B90), soit villes actives × 40 / 12 par mois ; volume à confirmer par les Ventes (D-16)</t>
+  </si>
+  <si>
+    <t>Calculé : soirées « place à l'unité » (ligne 11) des villes hors Paris situées en France (B97:B101) et actives (C97:C101). D-25 : villes 2 et 3. Seules ces soirées portent des frais de déplacement (ligne 29)</t>
+  </si>
+  <si>
+    <t>Calculé : idem pour les villes à l'étranger. D-25 : villes 4, 5 et 6. Prix, coûts et TVA supposés identiques à Paris (H)</t>
+  </si>
+  <si>
+    <t>Calculé : privatisations des villes hors Paris en France, 40 par ville active et par an (B90). Pas de frais de déplacement de production (décision du 28/10/2026)</t>
+  </si>
+  <si>
+    <t>Calculé : idem pour les villes à l'étranger. Pas de frais de déplacement de production ; prix, coûts et TVA identiques à Paris (H)</t>
+  </si>
+  <si>
+    <t>Repérage, déplacements, communication locale, recrutement des extras, conseils locaux : coût par ville en France (B86) ou à l'étranger (B87), réparti sur les 3 mois qui précèdent la première soirée (dates C97:C101). Calculé automatiquement</t>
+  </si>
+  <si>
+    <t>Apport initial (love money, D-26)</t>
+  </si>
+  <si>
+    <t>Décision D-26 (29/10/2026, matin) : mise de fonds initiale de 70 000 € en love money (apport des proches), en novembre 2026. Forme (capital, compte courant, BSA AIR) à définir par le Juridique ; aucun fonds versé</t>
+  </si>
+  <si>
+    <t>Ville (D-15, D-25)</t>
+  </si>
+  <si>
+    <t>Ville 3 (France)</t>
+  </si>
+  <si>
+    <t>Ville 4 (étranger)</t>
+  </si>
+  <si>
+    <t>D-25 : ville en France active dès novembre 2027 (D-21) ; ville à choisir par la Direction sur proposition du Marketing et des Ventes</t>
+  </si>
+  <si>
+    <t>D-25 : ville à l'étranger active dès novembre 2028 (D-21) ; ville à choisir par la Direction sur proposition du Marketing et des Ventes</t>
+  </si>
+  <si>
+    <t>H : idem, plus conseils juridiques et fiscaux locaux (Juridique, D-15 et D-25)</t>
+  </si>
+  <si>
+    <t>Pour changer une ouverture de ville : modifier le pays en B97:B101 et la date en C97:C101 (les lignes 14 à 17 et 52 se recalculent), puis les lignes 7 à 10 (valeurs saisies). Les totaux et le plan à 3 ans se recalculent.</t>
+  </si>
+  <si>
+    <t>D-15, D-21 et D-25 ; nouvelles villes actives en novembre</t>
+  </si>
+  <si>
+    <t>D-21 : 40 par ville active et par an dès l'année 2 ; volume à confirmer par les Ventes (D-16)</t>
+  </si>
+  <si>
+    <t>Trésorerie : point bas sur 36 mois (apport de 70 000 € en love money D-26, TVA et pré-vente compris, avant levée)</t>
+  </si>
+  <si>
+    <t>Décisions de la Direction : D-05 (28/10/2026, « Jauge - validé suivant fichier finance ») pour les places à l'unité, 40 / 35 / 30 couverts ; D-22 (28/10/2026, soir) pour la privatisation, 30 couverts</t>
+  </si>
+  <si>
+    <t>5 PRODUIT/Fou d'un soir le pricing.md (@Fréd, 27/10/2026) pour les places à l'unité ; décision D-22 pour la privatisation : 500 € TTC par convive, sans forfait. Minimum facturé de 30 couverts : point ouvert par la Direction (relevé du 29/10, § 3)</t>
+  </si>
+  <si>
+    <t>Décision D-22 (28/10/2026, soir) : forfait supprimé</t>
+  </si>
+  <si>
+    <t>Pop Tables · Pôle Finance · Version du 29/10/2026, selon les décisions D-02 à D-26. Remplace le modèle du 27/10 (rangé dans 2 FINANCE/OLD).</t>
+  </si>
+  <si>
+    <t>Budget revu par le responsable Finance le 28/10/2026 (soir), devenu référence décidée (D-21, D-22). Mis à jour le 29/10/2026 : villes 2 et 3 en France dès novembre 2027, villes 4 à 6 à l'étranger dès novembre 2028 (D-25) ; apport initial de 70 000 € en love money (D-26). Lignes 14 à 17 calculées à partir du calendrier des villes. Toutes les autres valeurs restent des hypothèses (H) : voir la fiche des données manquantes.</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1857,6 +1854,8 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2240,12 +2239,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13" x14ac:dyDescent="0.25">
@@ -2264,12 +2263,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="50" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="50" x14ac:dyDescent="0.25">
@@ -2277,7 +2276,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25" x14ac:dyDescent="0.25">
@@ -2341,7 +2340,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="25" x14ac:dyDescent="0.25">
@@ -2354,34 +2353,34 @@
     </row>
     <row r="17" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="50" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="50" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2481,13 +2480,13 @@
         <v>30</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -2513,7 +2512,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>83</v>
@@ -2546,7 +2545,7 @@
       <c r="H9" s="21"/>
       <c r="I9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>42</v>
       </c>
@@ -2569,13 +2568,13 @@
         <v>80</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>44</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>80</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="I11" s="20" t="s">
         <v>81</v>
@@ -2625,7 +2624,7 @@
         <v>82</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I12" s="20" t="s">
         <v>83</v>
@@ -2708,7 +2707,7 @@
         <v>82</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I15" s="20" t="s">
         <v>81</v>
@@ -2737,10 +2736,10 @@
         <v>82</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -2806,10 +2805,10 @@
         <v>82</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I19" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="50" x14ac:dyDescent="0.25">
@@ -2835,10 +2834,10 @@
         <v>82</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -2864,10 +2863,10 @@
         <v>82</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -2920,10 +2919,10 @@
         <v>82</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -2949,10 +2948,10 @@
         <v>82</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -2984,7 +2983,7 @@
     </row>
     <row r="26" spans="1:9" ht="50" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>51</v>
@@ -3006,13 +3005,13 @@
         <v>2008.9285714285711</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -3038,10 +3037,10 @@
         <v>82</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -3067,10 +3066,10 @@
         <v>82</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -3096,10 +3095,10 @@
         <v>82</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I29" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -3125,7 +3124,7 @@
         <v>82</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I30" s="20" t="s">
         <v>83</v>
@@ -3154,10 +3153,10 @@
         <v>82</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I31" s="20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -3189,7 +3188,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>51</v>
@@ -3207,13 +3206,13 @@
         <v>0</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -3502,17 +3501,17 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="38" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D4" s="45"/>
       <c r="E4" s="45"/>
@@ -3522,41 +3521,41 @@
         <v>80</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B7" s="42">
         <v>9</v>
@@ -3580,12 +3579,12 @@
         <v>0</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B8" s="42">
         <v>8</v>
@@ -3609,12 +3608,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B9" s="42">
         <v>7</v>
@@ -3638,12 +3637,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B10" s="42">
         <v>7</v>
@@ -3667,12 +3666,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B11" s="42">
         <v>7</v>
@@ -3696,12 +3695,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B12" s="42">
         <v>7</v>
@@ -3725,12 +3724,12 @@
         <v>0</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B13" s="42">
         <v>7</v>
@@ -3754,12 +3753,12 @@
         <v>0</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B14" s="42">
         <v>10</v>
@@ -3783,12 +3782,12 @@
         <v>0</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B15" s="42">
         <v>5</v>
@@ -3812,17 +3811,17 @@
         <v>0</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -3845,7 +3844,7 @@
     </row>
     <row r="19" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3868,7 +3867,7 @@
     </row>
     <row r="20" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3891,7 +3890,7 @@
     </row>
     <row r="21" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
@@ -3914,36 +3913,36 @@
     </row>
     <row r="23" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -3976,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -4009,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -4042,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -4075,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -4108,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -4141,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -4174,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -4207,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -4240,12 +4239,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4268,7 +4267,7 @@
     </row>
     <row r="37" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4291,7 +4290,7 @@
     </row>
     <row r="38" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4314,7 +4313,7 @@
     </row>
     <row r="39" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B39" s="39"/>
       <c r="C39" s="39"/>
@@ -4337,7 +4336,7 @@
     </row>
     <row r="40" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4360,12 +4359,12 @@
     </row>
     <row r="42" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4389,17 +4388,17 @@
   <sheetData>
     <row r="1" spans="1:43" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B3" s="53">
         <v>46327</v>
@@ -4407,7 +4406,7 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="D4" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E4" s="54">
         <v>1</v>
@@ -4523,13 +4522,13 @@
         <v>26</v>
       </c>
       <c r="B5" s="58" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="58" t="s">
         <v>270</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>271</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>272</v>
       </c>
       <c r="E5" s="51">
         <f t="shared" ref="E5:AN5" si="0">EDATE($B$3,E$4-1)</f>
@@ -4679,15 +4678,15 @@
         <v>32</v>
       </c>
       <c r="AP5" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AQ5" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -4734,7 +4733,7 @@
     </row>
     <row r="7" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B7" s="13">
         <f>P7</f>
@@ -4857,15 +4856,15 @@
         <v>6</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B8" s="13">
         <f t="shared" ref="B8:B19" si="1">SUM(E8:P8)</f>
@@ -4991,12 +4990,12 @@
         <v>82</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B9" s="13">
         <f t="shared" si="1"/>
@@ -5122,12 +5121,12 @@
         <v>82</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B10" s="13">
         <f t="shared" si="1"/>
@@ -5253,12 +5252,12 @@
         <v>82</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B11" s="13">
         <f t="shared" si="1"/>
@@ -5419,7 +5418,7 @@
     </row>
     <row r="12" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B12" s="13">
         <f t="shared" si="1"/>
@@ -5569,12 +5568,12 @@
         <v>82</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B13" s="13">
         <f t="shared" si="1"/>
@@ -5735,7 +5734,7 @@
     </row>
     <row r="14" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="B14" s="13">
         <f t="shared" si="1"/>
@@ -5743,130 +5742,166 @@
       </c>
       <c r="C14" s="13">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="E14" s="11">
-        <v>0</v>
-      </c>
-      <c r="F14" s="11">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0</v>
-      </c>
-      <c r="H14" s="11">
-        <v>0</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="11">
-        <v>0</v>
-      </c>
-      <c r="K14" s="11">
-        <v>0</v>
-      </c>
-      <c r="L14" s="11">
-        <v>0</v>
-      </c>
-      <c r="M14" s="11">
-        <v>0</v>
-      </c>
-      <c r="N14" s="11">
-        <v>0</v>
-      </c>
-      <c r="O14" s="11">
-        <v>0</v>
-      </c>
-      <c r="P14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>1</v>
-      </c>
-      <c r="R14" s="11">
-        <v>1</v>
-      </c>
-      <c r="S14" s="11">
-        <v>1</v>
-      </c>
-      <c r="T14" s="11">
-        <v>1</v>
-      </c>
-      <c r="U14" s="11">
-        <v>1</v>
-      </c>
-      <c r="V14" s="11">
-        <v>1</v>
-      </c>
-      <c r="W14" s="11">
-        <v>1</v>
-      </c>
-      <c r="X14" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="11">
+      <c r="E14" s="79">
+        <f t="shared" ref="E14:AN14" si="7">IF(E$7&lt;=1,0,E$11*SUMPRODUCT(($B$97:$B$101="France")*($C$97:$C$101&lt;=E$5))/E$7)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AD14" s="11">
+      <c r="R14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AE14" s="11">
+      <c r="S14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AF14" s="11">
+      <c r="T14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AG14" s="11">
+      <c r="U14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AH14" s="11">
+      <c r="V14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AI14" s="11">
+      <c r="W14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AJ14" s="11">
+      <c r="X14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AK14" s="11">
+      <c r="Y14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AL14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="11">
+      <c r="Z14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AN14" s="11">
+      <c r="AB14" s="79">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
+      <c r="AC14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AD14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AE14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AF14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AG14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AH14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AI14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AK14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AL14" s="79">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="AN14" s="79">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
       <c r="AO14" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B15" s="13">
         <f t="shared" si="1"/>
@@ -5874,130 +5909,166 @@
       </c>
       <c r="C15" s="13">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="E15" s="11">
-        <v>0</v>
-      </c>
-      <c r="F15" s="11">
-        <v>0</v>
-      </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11">
-        <v>0</v>
-      </c>
-      <c r="I15" s="11">
-        <v>0</v>
-      </c>
-      <c r="J15" s="11">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11">
-        <v>0</v>
-      </c>
-      <c r="P15" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>1</v>
-      </c>
-      <c r="R15" s="11">
-        <v>1</v>
-      </c>
-      <c r="S15" s="11">
-        <v>1</v>
-      </c>
-      <c r="T15" s="11">
-        <v>1</v>
-      </c>
-      <c r="U15" s="11">
-        <v>1</v>
-      </c>
-      <c r="V15" s="11">
-        <v>1</v>
-      </c>
-      <c r="W15" s="11">
-        <v>1</v>
-      </c>
-      <c r="X15" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="11">
+      <c r="E15" s="79">
+        <f t="shared" ref="E15:AN15" si="8">IF(E$7&lt;=1,0,E$11*SUMPRODUCT(($B$97:$B$101&lt;&gt;"France")*($C$97:$C$101&lt;=E$5))/E$7)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AD15" s="11">
+      <c r="AD15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AE15" s="11">
+      <c r="AE15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AF15" s="11">
+      <c r="AF15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AG15" s="11">
+      <c r="AG15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AH15" s="11">
+      <c r="AH15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AI15" s="11">
+      <c r="AI15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AJ15" s="11">
+      <c r="AJ15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AK15" s="11">
+      <c r="AK15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AL15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="11">
+      <c r="AL15" s="79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="AN15" s="11">
+      <c r="AN15" s="79">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>281</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B16" s="13">
         <f>SUM(E16:P16)</f>
@@ -6005,154 +6076,166 @@
       </c>
       <c r="C16" s="13">
         <f>SUM(Q16:AB16)</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D16" s="13">
         <f>SUM(AC16:AN16)</f>
         <v>80</v>
       </c>
-      <c r="E16" s="11">
-        <v>0</v>
-      </c>
-      <c r="F16" s="11">
-        <v>0</v>
-      </c>
-      <c r="G16" s="11">
-        <v>0</v>
-      </c>
-      <c r="H16" s="11">
-        <v>0</v>
-      </c>
-      <c r="I16" s="11">
-        <v>0</v>
-      </c>
-      <c r="J16" s="11">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11">
-        <v>0</v>
-      </c>
-      <c r="L16" s="11">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0</v>
-      </c>
-      <c r="O16" s="11">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="72">
-        <f>((Q$7&gt;=2)+(Q$7&gt;=4))*$B$90/12</f>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="R16" s="72">
-        <f t="shared" ref="R16:AN16" si="7">((R$7&gt;=2)+(R$7&gt;=4))*$B$90/12</f>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="S16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="T16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="U16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="V16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="W16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="X16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="Y16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="Z16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AA16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AB16" s="72">
-        <f t="shared" si="7"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AC16" s="72">
-        <f t="shared" si="7"/>
+      <c r="E16" s="79">
+        <f t="shared" ref="E16:AN16" si="9">SUMPRODUCT(($B$97:$B$101="France")*($C$97:$C$101&lt;=E$5))*$B$90/12</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AD16" s="72">
-        <f t="shared" si="7"/>
+      <c r="R16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AE16" s="72">
-        <f t="shared" si="7"/>
+      <c r="S16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AF16" s="72">
-        <f t="shared" si="7"/>
+      <c r="T16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AG16" s="72">
-        <f t="shared" si="7"/>
+      <c r="U16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AH16" s="72">
-        <f t="shared" si="7"/>
+      <c r="V16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AI16" s="72">
-        <f t="shared" si="7"/>
+      <c r="W16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AJ16" s="72">
-        <f t="shared" si="7"/>
+      <c r="X16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AK16" s="72">
-        <f t="shared" si="7"/>
+      <c r="Y16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AL16" s="72">
-        <f t="shared" si="7"/>
+      <c r="Z16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AM16" s="72">
-        <f t="shared" si="7"/>
+      <c r="AA16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="AN16" s="72">
-        <f t="shared" si="7"/>
+      <c r="AB16" s="80">
+        <f t="shared" si="9"/>
         <v>6.666666666666667</v>
       </c>
+      <c r="AC16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AD16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AE16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AF16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AG16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AH16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AI16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AJ16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AK16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AL16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AM16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="AN16" s="80">
+        <f t="shared" si="9"/>
+        <v>6.666666666666667</v>
+      </c>
       <c r="AO16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B17" s="13">
         <f>SUM(E17:P17)</f>
@@ -6160,154 +6243,166 @@
       </c>
       <c r="C17" s="13">
         <f>SUM(Q17:AB17)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D17" s="13">
         <f>SUM(AC17:AN17)</f>
         <v>120</v>
       </c>
-      <c r="E17" s="11">
-        <v>0</v>
-      </c>
-      <c r="F17" s="11">
-        <v>0</v>
-      </c>
-      <c r="G17" s="11">
-        <v>0</v>
-      </c>
-      <c r="H17" s="11">
-        <v>0</v>
-      </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="11">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11">
-        <v>0</v>
-      </c>
-      <c r="M17" s="11">
-        <v>0</v>
-      </c>
-      <c r="N17" s="11">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11">
-        <v>0</v>
-      </c>
-      <c r="P17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="72">
-        <f>((Q$7&gt;=3)+(Q$7&gt;=5)+(Q$7&gt;=6))*$B$90/12</f>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="R17" s="72">
-        <f t="shared" ref="R17:AN17" si="8">((R$7&gt;=3)+(R$7&gt;=5)+(R$7&gt;=6))*$B$90/12</f>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="S17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="T17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="U17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="V17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="W17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="X17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="Y17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="Z17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AA17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AB17" s="72">
-        <f t="shared" si="8"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="AC17" s="72">
-        <f t="shared" si="8"/>
+      <c r="E17" s="79">
+        <f t="shared" ref="E17:AN17" si="10">SUMPRODUCT(($B$97:$B$101&lt;&gt;"France")*($C$97:$C$101&lt;=E$5))*$B$90/12</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="79">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="80">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AD17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AD17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AE17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AE17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AF17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AF17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AG17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AG17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AH17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AH17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AI17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AI17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AJ17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AJ17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AK17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AK17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AL17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AL17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AM17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AM17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="AN17" s="72">
-        <f t="shared" si="8"/>
+      <c r="AN17" s="80">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B18" s="13">
         <f t="shared" si="1"/>
@@ -6433,12 +6528,12 @@
         <v>80</v>
       </c>
       <c r="AP18" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B19" s="13">
         <f t="shared" si="1"/>
@@ -6564,12 +6659,12 @@
         <v>80</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="B20" s="13">
         <f>MAX(E20:P20)</f>
@@ -6728,15 +6823,15 @@
         <v>6</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP20" s="1" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="B21" s="13">
         <f>MAX(E21:P21)</f>
@@ -6895,15 +6990,15 @@
         <v>6</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP21" s="1" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="B22" s="13">
         <f>MAX(E22:P22)</f>
@@ -7062,15 +7157,15 @@
         <v>15</v>
       </c>
       <c r="AO22" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -7117,18 +7212,18 @@
     </row>
     <row r="24" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B24" s="16">
-        <f t="shared" ref="B24:B31" si="9">SUM(E24:P24)</f>
+        <f t="shared" ref="B24:B31" si="11">SUM(E24:P24)</f>
         <v>125892.85714285713</v>
       </c>
       <c r="C24" s="16">
-        <f t="shared" ref="C24:C31" si="10">SUM(Q24:AB24)</f>
+        <f t="shared" ref="C24:C31" si="12">SUM(Q24:AB24)</f>
         <v>461607.14285714272</v>
       </c>
       <c r="D24" s="16">
-        <f t="shared" ref="D24:D31" si="11">SUM(AC24:AN24)</f>
+        <f t="shared" ref="D24:D31" si="13">SUM(AC24:AN24)</f>
         <v>923214.28571428545</v>
       </c>
       <c r="E24" s="15">
@@ -7276,23 +7371,23 @@
         <v>83928.57142857142</v>
       </c>
       <c r="AP24" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B25" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>93750</v>
       </c>
       <c r="C25" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1607142.8571428566</v>
       </c>
       <c r="D25" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3214285.7142857132</v>
       </c>
       <c r="E25" s="15">
@@ -7442,179 +7537,179 @@
     </row>
     <row r="26" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>219642.8571428571</v>
       </c>
       <c r="C26" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2068749.9999999993</v>
       </c>
       <c r="D26" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4137499.9999999986</v>
       </c>
       <c r="E26" s="16">
-        <f t="shared" ref="E26:AN26" si="12">E24+E25</f>
+        <f t="shared" ref="E26:AN26" si="14">E24+E25</f>
         <v>0</v>
       </c>
       <c r="F26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>10357.142857142855</v>
       </c>
       <c r="H26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>18482.142857142855</v>
       </c>
       <c r="I26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13124.999999999998</v>
       </c>
       <c r="J26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>23749.999999999996</v>
       </c>
       <c r="K26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>31874.999999999996</v>
       </c>
       <c r="L26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>26517.857142857138</v>
       </c>
       <c r="M26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>10357.142857142855</v>
       </c>
       <c r="N26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>45267.857142857138</v>
       </c>
       <c r="P26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>39910.714285714283</v>
       </c>
       <c r="Q26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="R26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="S26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="T26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="U26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="V26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="W26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="X26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="Y26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="Z26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>133928.57142857142</v>
       </c>
       <c r="AA26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="AB26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>175892.85714285713</v>
       </c>
       <c r="AC26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AD26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AE26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AF26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AG26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AH26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AI26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AJ26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AK26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AL26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>267857.14285714284</v>
       </c>
       <c r="AM26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
       <c r="AN26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>351785.71428571426</v>
       </c>
     </row>
     <row r="27" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B27" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>161190.3571428571</v>
       </c>
       <c r="C27" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1433293.2142857141</v>
       </c>
       <c r="D27" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2866586.4285714282</v>
       </c>
       <c r="E27" s="15">
@@ -7762,23 +7857,23 @@
         <v>244364.99999999997</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B28" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1155</v>
       </c>
       <c r="C28" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D28" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E28" s="15">
@@ -7929,174 +8024,174 @@
         <v>82</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B29" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="C29" s="16">
-        <f t="shared" si="10"/>
-        <v>11000</v>
+        <f t="shared" si="12"/>
+        <v>6600</v>
       </c>
       <c r="D29" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>29700</v>
       </c>
       <c r="E29" s="15">
-        <f t="shared" ref="E29:AN29" si="13">E14*$B$84+E15*$B$85</f>
+        <f t="shared" ref="E29:AN29" si="15">E14*$B$84+E15*$B$85</f>
         <v>0</v>
       </c>
       <c r="F29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="R29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="S29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="T29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="U29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="V29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="W29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="X29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="Y29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="Z29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="AB29" s="15">
-        <f t="shared" si="13"/>
-        <v>1000</v>
+        <f t="shared" si="15"/>
+        <v>600</v>
       </c>
       <c r="AC29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AD29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AE29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AF29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AG29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AH29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AI29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AJ29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AK29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AL29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AM29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AN29" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2700</v>
       </c>
       <c r="AO29" s="1" t="s">
         <v>82</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AQ29" s="55">
         <v>0.1</v>
@@ -8107,159 +8202,159 @@
         <v>70</v>
       </c>
       <c r="B30" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>162345.3571428571</v>
       </c>
       <c r="C30" s="16">
-        <f t="shared" si="10"/>
-        <v>1444293.2142857141</v>
+        <f t="shared" si="12"/>
+        <v>1439893.2142857141</v>
       </c>
       <c r="D30" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2896286.4285714282</v>
       </c>
       <c r="E30" s="16">
-        <f t="shared" ref="E30:AN30" si="14">E27+E28+E29</f>
+        <f t="shared" ref="E30:AN30" si="16">E27+E28+E29</f>
         <v>0</v>
       </c>
       <c r="F30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>8269.2857142857138</v>
       </c>
       <c r="H30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>14871.25</v>
       </c>
       <c r="I30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>10911.25</v>
       </c>
       <c r="J30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>16497.857142857141</v>
       </c>
       <c r="K30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>23344.821428571428</v>
       </c>
       <c r="L30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>19839.821428571428</v>
       </c>
       <c r="M30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>7569.2857142857138</v>
       </c>
       <c r="N30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>32273.392857142855</v>
       </c>
       <c r="P30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>28768.392857142855</v>
       </c>
       <c r="Q30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="R30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="S30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="T30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="U30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="V30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="W30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="X30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="Y30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="Z30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>89285.714285714275</v>
       </c>
       <c r="AA30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="AB30" s="16">
-        <f t="shared" si="14"/>
-        <v>123182.49999999999</v>
+        <f t="shared" si="16"/>
+        <v>122782.49999999999</v>
       </c>
       <c r="AC30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AD30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AE30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AF30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AG30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AH30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AI30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AJ30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AK30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AL30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>178571.42857142855</v>
       </c>
       <c r="AM30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AN30" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>247064.99999999997</v>
       </c>
       <c r="AQ30" s="55"/>
@@ -8269,166 +8364,166 @@
         <v>72</v>
       </c>
       <c r="B31" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>57297.499999999985</v>
       </c>
       <c r="C31" s="16">
-        <f t="shared" si="10"/>
-        <v>624456.7857142858</v>
+        <f t="shared" si="12"/>
+        <v>628856.7857142858</v>
       </c>
       <c r="D31" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1241213.5714285716</v>
       </c>
       <c r="E31" s="16">
-        <f t="shared" ref="E31:AN31" si="15">E26-E30</f>
+        <f t="shared" ref="E31:AN31" si="17">E26-E30</f>
         <v>0</v>
       </c>
       <c r="F31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2087.8571428571413</v>
       </c>
       <c r="H31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3610.8928571428551</v>
       </c>
       <c r="I31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2213.7499999999982</v>
       </c>
       <c r="J31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>7252.1428571428551</v>
       </c>
       <c r="K31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8530.1785714285688</v>
       </c>
       <c r="L31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6678.0357142857101</v>
       </c>
       <c r="M31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2787.8571428571413</v>
       </c>
       <c r="N31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12994.464285714283</v>
       </c>
       <c r="P31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11142.321428571428</v>
       </c>
       <c r="Q31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="R31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="S31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="T31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="U31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="V31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="W31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="X31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="Y31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="Z31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>44642.857142857145</v>
       </c>
       <c r="AA31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="AB31" s="16">
-        <f t="shared" si="15"/>
-        <v>52710.357142857145</v>
+        <f t="shared" si="17"/>
+        <v>53110.357142857145</v>
       </c>
       <c r="AC31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AD31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AE31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AF31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AG31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AH31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AI31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AJ31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AK31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AL31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>89285.71428571429</v>
       </c>
       <c r="AM31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AN31" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>104720.71428571429</v>
       </c>
       <c r="AQ31" s="55"/>
     </row>
     <row r="32" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -8638,7 +8733,7 @@
         <v>82</v>
       </c>
       <c r="AP33" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AQ33" s="55"/>
     </row>
@@ -8804,10 +8899,10 @@
         <v>16243.073999999999</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP34" s="1" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="AQ34" s="55"/>
     </row>
@@ -8973,10 +9068,10 @@
         <v>24360</v>
       </c>
       <c r="AO35" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP35" s="1" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="AQ35" s="55"/>
     </row>
@@ -9145,13 +9240,13 @@
         <v>82</v>
       </c>
       <c r="AP36" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AQ36" s="55"/>
     </row>
     <row r="37" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B37" s="16">
         <f>SUM(E37:P37)</f>
@@ -9170,150 +9265,150 @@
         <v>0</v>
       </c>
       <c r="F37" s="16">
-        <f t="shared" ref="F37:AN37" si="16">SUM(F33:F36)</f>
+        <f t="shared" ref="F37:AN37" si="18">SUM(F33:F36)</f>
         <v>0</v>
       </c>
       <c r="G37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="R37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="S37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="T37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="U37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="V37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="W37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="X37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="Y37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="Z37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="AA37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="AB37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8121.5369999999994</v>
       </c>
       <c r="AC37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AD37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AE37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AF37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AG37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AH37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AI37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AJ37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AK37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AL37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AM37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AN37" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>53653.074000000001</v>
       </c>
       <c r="AQ37" s="55"/>
     </row>
     <row r="38" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -9360,18 +9455,18 @@
     </row>
     <row r="39" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B39" s="16">
-        <f t="shared" ref="B39:B57" si="17">SUM(E39:P39)</f>
+        <f t="shared" ref="B39:B57" si="19">SUM(E39:P39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="16">
-        <f t="shared" ref="C39:C57" si="18">SUM(Q39:AB39)</f>
+        <f t="shared" ref="C39:C57" si="20">SUM(Q39:AB39)</f>
         <v>10800</v>
       </c>
       <c r="D39" s="16">
-        <f t="shared" ref="D39:D57" si="19">SUM(AC39:AN39)</f>
+        <f t="shared" ref="D39:D57" si="21">SUM(AC39:AN39)</f>
         <v>54000</v>
       </c>
       <c r="E39" s="78">
@@ -9379,150 +9474,150 @@
         <v>0</v>
       </c>
       <c r="F39" s="78">
-        <f t="shared" ref="F39:AN39" si="20">F$22*$B$91</f>
+        <f t="shared" ref="F39:AN39" si="22">F$22*$B$91</f>
         <v>0</v>
       </c>
       <c r="G39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="O39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="P39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="R39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="S39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="T39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="U39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="V39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="W39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="X39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="Y39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="Z39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="AA39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="AB39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>900</v>
       </c>
       <c r="AC39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AD39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AE39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AF39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AG39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AH39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AI39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AJ39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AK39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AL39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AM39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AN39" s="78">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4500</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP39" s="1" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="AQ39" s="57">
         <f>TVA!$C$30</f>
@@ -9531,10 +9626,10 @@
     </row>
     <row r="40" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B40" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>960</v>
       </c>
       <c r="C40" s="16">
@@ -9542,7 +9637,7 @@
         <v>2760</v>
       </c>
       <c r="D40" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>9960</v>
       </c>
       <c r="E40" s="78">
@@ -9550,150 +9645,150 @@
         <v>80</v>
       </c>
       <c r="F40" s="78">
-        <f t="shared" ref="F40:AN40" si="21">$B$92+F$22*$B$93</f>
+        <f t="shared" ref="F40:AN40" si="23">$B$92+F$22*$B$93</f>
         <v>80</v>
       </c>
       <c r="G40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="H40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="I40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="J40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="K40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="L40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="M40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="N40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="O40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="P40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="Q40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="R40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="S40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="T40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="U40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="V40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="W40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="X40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="Y40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="Z40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="AA40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="AB40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>230</v>
       </c>
       <c r="AC40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AD40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AE40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AF40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AG40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AH40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AI40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AJ40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AK40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AL40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AM40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AN40" s="78">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>830</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP40" s="1" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="AQ40" s="57">
         <f>TVA!$C$31</f>
@@ -9702,18 +9797,18 @@
     </row>
     <row r="41" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B41" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>7200</v>
       </c>
       <c r="C41" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15000</v>
       </c>
       <c r="D41" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>30000</v>
       </c>
       <c r="E41" s="14">
@@ -9828,7 +9923,7 @@
         <v>82</v>
       </c>
       <c r="AP41" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AQ41" s="57">
         <f>TVA!$C$32</f>
@@ -9837,18 +9932,18 @@
     </row>
     <row r="42" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B42" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>10000</v>
       </c>
       <c r="C42" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D42" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E42" s="14">
@@ -9963,7 +10058,7 @@
         <v>82</v>
       </c>
       <c r="AP42" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AQ42" s="57">
         <v>0.2</v>
@@ -9971,18 +10066,18 @@
     </row>
     <row r="43" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B43" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>28000</v>
       </c>
       <c r="C43" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D43" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E43" s="14">
@@ -10097,7 +10192,7 @@
         <v>82</v>
       </c>
       <c r="AP43" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AQ43" s="57">
         <v>0.1</v>
@@ -10105,152 +10200,152 @@
     </row>
     <row r="44" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B44" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1200</v>
       </c>
       <c r="C44" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2400</v>
       </c>
       <c r="D44" s="16">
+        <f t="shared" si="21"/>
+        <v>3600</v>
+      </c>
+      <c r="E44" s="14">
+        <v>100</v>
+      </c>
+      <c r="F44" s="14">
+        <v>100</v>
+      </c>
+      <c r="G44" s="14">
+        <v>100</v>
+      </c>
+      <c r="H44" s="14">
+        <v>100</v>
+      </c>
+      <c r="I44" s="14">
+        <v>100</v>
+      </c>
+      <c r="J44" s="14">
+        <v>100</v>
+      </c>
+      <c r="K44" s="14">
+        <v>100</v>
+      </c>
+      <c r="L44" s="14">
+        <v>100</v>
+      </c>
+      <c r="M44" s="14">
+        <v>100</v>
+      </c>
+      <c r="N44" s="14">
+        <v>100</v>
+      </c>
+      <c r="O44" s="14">
+        <v>100</v>
+      </c>
+      <c r="P44" s="14">
+        <v>100</v>
+      </c>
+      <c r="Q44" s="14">
+        <v>200</v>
+      </c>
+      <c r="R44" s="14">
+        <v>200</v>
+      </c>
+      <c r="S44" s="14">
+        <v>200</v>
+      </c>
+      <c r="T44" s="14">
+        <v>200</v>
+      </c>
+      <c r="U44" s="14">
+        <v>200</v>
+      </c>
+      <c r="V44" s="14">
+        <v>200</v>
+      </c>
+      <c r="W44" s="14">
+        <v>200</v>
+      </c>
+      <c r="X44" s="14">
+        <v>200</v>
+      </c>
+      <c r="Y44" s="14">
+        <v>200</v>
+      </c>
+      <c r="Z44" s="14">
+        <v>200</v>
+      </c>
+      <c r="AA44" s="14">
+        <v>200</v>
+      </c>
+      <c r="AB44" s="14">
+        <v>200</v>
+      </c>
+      <c r="AC44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AD44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AE44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AF44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AG44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AH44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AI44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AJ44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AK44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AL44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AM44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AN44" s="14">
+        <v>300</v>
+      </c>
+      <c r="AO44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP44" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="AQ44" s="57">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:43" ht="13" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B45" s="16">
         <f t="shared" si="19"/>
         <v>3600</v>
       </c>
-      <c r="E44" s="14">
-        <v>100</v>
-      </c>
-      <c r="F44" s="14">
-        <v>100</v>
-      </c>
-      <c r="G44" s="14">
-        <v>100</v>
-      </c>
-      <c r="H44" s="14">
-        <v>100</v>
-      </c>
-      <c r="I44" s="14">
-        <v>100</v>
-      </c>
-      <c r="J44" s="14">
-        <v>100</v>
-      </c>
-      <c r="K44" s="14">
-        <v>100</v>
-      </c>
-      <c r="L44" s="14">
-        <v>100</v>
-      </c>
-      <c r="M44" s="14">
-        <v>100</v>
-      </c>
-      <c r="N44" s="14">
-        <v>100</v>
-      </c>
-      <c r="O44" s="14">
-        <v>100</v>
-      </c>
-      <c r="P44" s="14">
-        <v>100</v>
-      </c>
-      <c r="Q44" s="14">
-        <v>200</v>
-      </c>
-      <c r="R44" s="14">
-        <v>200</v>
-      </c>
-      <c r="S44" s="14">
-        <v>200</v>
-      </c>
-      <c r="T44" s="14">
-        <v>200</v>
-      </c>
-      <c r="U44" s="14">
-        <v>200</v>
-      </c>
-      <c r="V44" s="14">
-        <v>200</v>
-      </c>
-      <c r="W44" s="14">
-        <v>200</v>
-      </c>
-      <c r="X44" s="14">
-        <v>200</v>
-      </c>
-      <c r="Y44" s="14">
-        <v>200</v>
-      </c>
-      <c r="Z44" s="14">
-        <v>200</v>
-      </c>
-      <c r="AA44" s="14">
-        <v>200</v>
-      </c>
-      <c r="AB44" s="14">
-        <v>200</v>
-      </c>
-      <c r="AC44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AD44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AE44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AF44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AG44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AH44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AI44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AJ44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AK44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AL44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AM44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AN44" s="14">
-        <v>300</v>
-      </c>
-      <c r="AO44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP44" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AQ44" s="57">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:43" ht="13" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B45" s="16">
-        <f t="shared" si="17"/>
-        <v>3600</v>
-      </c>
       <c r="C45" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7200</v>
       </c>
       <c r="D45" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12000</v>
       </c>
       <c r="E45" s="14">
@@ -10365,7 +10460,7 @@
         <v>82</v>
       </c>
       <c r="AP45" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AQ45" s="57">
         <v>0.1</v>
@@ -10373,18 +10468,18 @@
     </row>
     <row r="46" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B46" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>765</v>
       </c>
       <c r="C46" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2805</v>
       </c>
       <c r="D46" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>5610</v>
       </c>
       <c r="E46" s="15">
@@ -10535,7 +10630,7 @@
         <v>82</v>
       </c>
       <c r="AP46" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AQ46" s="57">
         <v>0.1</v>
@@ -10543,18 +10638,18 @@
     </row>
     <row r="47" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B47" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2500</v>
       </c>
       <c r="C47" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>5000.0000000000045</v>
       </c>
       <c r="D47" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>8000.0000000000036</v>
       </c>
       <c r="E47" s="14">
@@ -10669,7 +10764,7 @@
         <v>82</v>
       </c>
       <c r="AP47" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AQ47" s="57">
         <v>0.2</v>
@@ -10677,169 +10772,169 @@
     </row>
     <row r="48" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B48" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4392.8571428571422</v>
       </c>
       <c r="C48" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>41375</v>
       </c>
       <c r="D48" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>82750</v>
       </c>
       <c r="E48" s="15">
-        <f t="shared" ref="E48:AN48" si="22">$B$89*E26</f>
+        <f t="shared" ref="E48:AN48" si="24">$B$89*E26</f>
         <v>0</v>
       </c>
       <c r="F48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>207.14285714285711</v>
       </c>
       <c r="H48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>369.64285714285711</v>
       </c>
       <c r="I48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>262.49999999999994</v>
       </c>
       <c r="J48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>474.99999999999994</v>
       </c>
       <c r="K48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>637.49999999999989</v>
       </c>
       <c r="L48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>530.35714285714278</v>
       </c>
       <c r="M48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>207.14285714285711</v>
       </c>
       <c r="N48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>905.35714285714278</v>
       </c>
       <c r="P48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>798.21428571428567</v>
       </c>
       <c r="Q48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="R48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="S48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="T48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="U48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="V48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="W48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="X48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="Y48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="Z48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>2678.5714285714284</v>
       </c>
       <c r="AA48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="AB48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3517.8571428571427</v>
       </c>
       <c r="AC48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AD48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AE48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AF48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AG48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AH48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AI48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AJ48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AK48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AL48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>5357.1428571428569</v>
       </c>
       <c r="AM48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AN48" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7035.7142857142853</v>
       </c>
       <c r="AO48" s="1" t="s">
         <v>82</v>
       </c>
       <c r="AP48" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AQ48" s="57">
         <f>TVA!$C$33</f>
@@ -10848,18 +10943,18 @@
     </row>
     <row r="49" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B49" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2700</v>
       </c>
       <c r="C49" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3999.9999999999959</v>
       </c>
       <c r="D49" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>6000</v>
       </c>
       <c r="E49" s="14">
@@ -10974,7 +11069,7 @@
         <v>82</v>
       </c>
       <c r="AP49" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AQ49" s="57">
         <f>TVA!$C$34</f>
@@ -10983,18 +11078,18 @@
     </row>
     <row r="50" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B50" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>360</v>
       </c>
       <c r="C50" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>600</v>
       </c>
       <c r="D50" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>999.99999999999943</v>
       </c>
       <c r="E50" s="14">
@@ -11109,7 +11204,7 @@
         <v>82</v>
       </c>
       <c r="AP50" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AQ50" s="57">
         <f>TVA!$C$35</f>
@@ -11118,18 +11213,18 @@
     </row>
     <row r="51" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B51" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>600</v>
       </c>
       <c r="C51" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2000.0000000000039</v>
       </c>
       <c r="D51" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>3999.9999999999959</v>
       </c>
       <c r="E51" s="14">
@@ -11244,7 +11339,7 @@
         <v>82</v>
       </c>
       <c r="AP51" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AQ51" s="57">
         <f>TVA!$C$36</f>
@@ -11253,18 +11348,18 @@
     </row>
     <row r="52" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B52" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>30000</v>
       </c>
       <c r="C52" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>45000</v>
       </c>
       <c r="D52" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E52" s="14" cm="1">
@@ -11412,10 +11507,10 @@
         <v>0</v>
       </c>
       <c r="AO52" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP52" s="1" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="AQ52" s="57">
         <v>0.1</v>
@@ -11423,18 +11518,18 @@
     </row>
     <row r="53" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B53" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1000</v>
       </c>
       <c r="C53" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D53" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E53" s="14">
@@ -11549,7 +11644,7 @@
         <v>82</v>
       </c>
       <c r="AP53" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AQ53" s="57">
         <v>0</v>
@@ -11557,18 +11652,18 @@
     </row>
     <row r="54" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B54" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="C54" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>300</v>
       </c>
       <c r="D54" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>600</v>
       </c>
       <c r="E54" s="14">
@@ -11683,7 +11778,7 @@
         <v>82</v>
       </c>
       <c r="AP54" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AQ54" s="57">
         <v>0</v>
@@ -11691,18 +11786,18 @@
     </row>
     <row r="55" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B55" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>252</v>
       </c>
       <c r="C55" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D55" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>999.99999999999943</v>
       </c>
       <c r="E55" s="14">
@@ -11817,7 +11912,7 @@
         <v>82</v>
       </c>
       <c r="AP55" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AQ55" s="57">
         <f>TVA!$C$37</f>
@@ -11826,331 +11921,331 @@
     </row>
     <row r="56" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B56" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>93529.857142857145</v>
       </c>
       <c r="C56" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>139240</v>
       </c>
       <c r="D56" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>218519.99999999997</v>
       </c>
       <c r="E56" s="16">
-        <f t="shared" ref="E56:AN56" si="23">SUM(E39:E55)</f>
+        <f t="shared" ref="E56:AN56" si="25">SUM(E39:E55)</f>
         <v>2712</v>
       </c>
       <c r="F56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4660</v>
       </c>
       <c r="G56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2452.1428571428569</v>
       </c>
       <c r="H56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7614.6428571428569</v>
       </c>
       <c r="I56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>34307.5</v>
       </c>
       <c r="J56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2520</v>
       </c>
       <c r="K56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1682.5</v>
       </c>
       <c r="L56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1575.3571428571427</v>
       </c>
       <c r="M56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1252.1428571428571</v>
       </c>
       <c r="N56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10960</v>
       </c>
       <c r="O56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>11950.357142857143</v>
       </c>
       <c r="P56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>11843.214285714286</v>
       </c>
       <c r="Q56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="R56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>8219.5238095238092</v>
       </c>
       <c r="S56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="T56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="U56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="V56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="W56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="X56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="Y56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7919.5238095238092</v>
       </c>
       <c r="Z56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>21825.238095238095</v>
       </c>
       <c r="AA56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>22919.523809523809</v>
       </c>
       <c r="AB56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>22919.523809523809</v>
       </c>
       <c r="AC56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AD56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18942.38095238095</v>
       </c>
       <c r="AE56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AF56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AG56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AH56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AI56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AJ56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AK56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AL56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>16153.809523809525</v>
       </c>
       <c r="AM56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AN56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>18342.38095238095</v>
       </c>
       <c r="AQ56" s="55"/>
     </row>
     <row r="57" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B57" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>93529.857142857145</v>
       </c>
       <c r="C57" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>236698.44399999999</v>
       </c>
       <c r="D57" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>862356.88800000004</v>
       </c>
       <c r="E57" s="16">
-        <f t="shared" ref="E57:AN57" si="24">E37+E56</f>
+        <f t="shared" ref="E57:AN57" si="26">E37+E56</f>
         <v>2712</v>
       </c>
       <c r="F57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4660</v>
       </c>
       <c r="G57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2452.1428571428569</v>
       </c>
       <c r="H57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>7614.6428571428569</v>
       </c>
       <c r="I57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34307.5</v>
       </c>
       <c r="J57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2520</v>
       </c>
       <c r="K57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1682.5</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1575.3571428571427</v>
       </c>
       <c r="M57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1252.1428571428571</v>
       </c>
       <c r="N57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>10960</v>
       </c>
       <c r="O57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>11950.357142857143</v>
       </c>
       <c r="P57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>11843.214285714286</v>
       </c>
       <c r="Q57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="R57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16341.060809523809</v>
       </c>
       <c r="S57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="T57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="U57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="V57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="W57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="X57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="Y57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16041.060809523809</v>
       </c>
       <c r="Z57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>29946.775095238096</v>
       </c>
       <c r="AA57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>31041.060809523809</v>
       </c>
       <c r="AB57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>31041.060809523809</v>
       </c>
       <c r="AC57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AD57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>72595.454952380955</v>
       </c>
       <c r="AE57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AF57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AG57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AH57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AI57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AJ57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AK57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AL57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>69806.88352380952</v>
       </c>
       <c r="AM57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AN57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>71995.454952380955</v>
       </c>
       <c r="AQ57" s="55"/>
     </row>
     <row r="58" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -12197,7 +12292,7 @@
     </row>
     <row r="59" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B59" s="16">
         <f>SUM(E59:P59)</f>
@@ -12205,161 +12300,161 @@
       </c>
       <c r="C59" s="16">
         <f>SUM(Q59:AB59)</f>
-        <v>387758.34171428578</v>
+        <v>392158.34171428578</v>
       </c>
       <c r="D59" s="16">
         <f>SUM(AC59:AN59)</f>
         <v>378856.68342857156</v>
       </c>
       <c r="E59" s="16">
-        <f t="shared" ref="E59:AN59" si="25">E31-E57</f>
+        <f t="shared" ref="E59:AN59" si="27">E31-E57</f>
         <v>-2712</v>
       </c>
       <c r="F59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-4660</v>
       </c>
       <c r="G59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-364.28571428571558</v>
       </c>
       <c r="H59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-4003.7500000000018</v>
       </c>
       <c r="I59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-32093.75</v>
       </c>
       <c r="J59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4732.1428571428551</v>
       </c>
       <c r="K59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>6847.6785714285688</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5102.678571428567</v>
       </c>
       <c r="M59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1535.7142857142842</v>
       </c>
       <c r="N59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-10960</v>
       </c>
       <c r="O59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1044.1071428571395</v>
       </c>
       <c r="P59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-700.8928571428587</v>
       </c>
       <c r="Q59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="R59" s="16">
-        <f t="shared" si="25"/>
-        <v>36369.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>36769.296333333332</v>
       </c>
       <c r="S59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="T59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="U59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="V59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="W59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="X59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="Y59" s="16">
-        <f t="shared" si="25"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="27"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="Z59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>14696.082047619049</v>
       </c>
       <c r="AA59" s="16">
-        <f t="shared" si="25"/>
-        <v>21669.296333333335</v>
+        <f t="shared" si="27"/>
+        <v>22069.296333333335</v>
       </c>
       <c r="AB59" s="16">
-        <f t="shared" si="25"/>
-        <v>21669.296333333335</v>
+        <f t="shared" si="27"/>
+        <v>22069.296333333335</v>
       </c>
       <c r="AC59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AD59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32125.259333333335</v>
       </c>
       <c r="AE59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AF59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AG59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AH59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AI59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AJ59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AK59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AL59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>19478.83076190477</v>
       </c>
       <c r="AM59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AN59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AQ59" s="55"/>
     </row>
     <row r="60" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B60" s="16">
         <f>P60</f>
@@ -12367,161 +12462,161 @@
       </c>
       <c r="C60" s="16">
         <f>AB60</f>
-        <v>351525.98457142862</v>
+        <v>355925.98457142862</v>
       </c>
       <c r="D60" s="16">
         <f>AN60</f>
-        <v>730382.6680000003</v>
+        <v>734782.6680000003</v>
       </c>
       <c r="E60" s="15">
         <f>E59</f>
         <v>-2712</v>
       </c>
       <c r="F60" s="15">
-        <f t="shared" ref="F60:AN60" si="26">E60+F59</f>
+        <f t="shared" ref="F60:AN60" si="28">E60+F59</f>
         <v>-7372</v>
       </c>
       <c r="G60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-7736.2857142857156</v>
       </c>
       <c r="H60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-11740.035714285717</v>
       </c>
       <c r="I60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-43833.785714285717</v>
       </c>
       <c r="J60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-39101.642857142862</v>
       </c>
       <c r="K60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-32253.964285714294</v>
       </c>
       <c r="L60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-27151.285714285725</v>
       </c>
       <c r="M60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-25615.571428571442</v>
       </c>
       <c r="N60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-36575.571428571442</v>
       </c>
       <c r="O60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-35531.464285714304</v>
       </c>
       <c r="P60" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-36232.357142857159</v>
       </c>
       <c r="Q60" s="15">
-        <f t="shared" si="26"/>
-        <v>436.93919047617237</v>
+        <f t="shared" si="28"/>
+        <v>836.93919047617237</v>
       </c>
       <c r="R60" s="15">
-        <f t="shared" si="26"/>
-        <v>36806.235523809504</v>
+        <f t="shared" si="28"/>
+        <v>37606.235523809504</v>
       </c>
       <c r="S60" s="15">
-        <f t="shared" si="26"/>
-        <v>73475.531857142836</v>
+        <f t="shared" si="28"/>
+        <v>74675.531857142836</v>
       </c>
       <c r="T60" s="15">
-        <f t="shared" si="26"/>
-        <v>110144.82819047617</v>
+        <f t="shared" si="28"/>
+        <v>111744.82819047617</v>
       </c>
       <c r="U60" s="15">
-        <f t="shared" si="26"/>
-        <v>146814.1245238095</v>
+        <f t="shared" si="28"/>
+        <v>148814.1245238095</v>
       </c>
       <c r="V60" s="15">
-        <f t="shared" si="26"/>
-        <v>183483.42085714283</v>
+        <f t="shared" si="28"/>
+        <v>185883.42085714283</v>
       </c>
       <c r="W60" s="15">
-        <f t="shared" si="26"/>
-        <v>220152.71719047616</v>
+        <f t="shared" si="28"/>
+        <v>222952.71719047616</v>
       </c>
       <c r="X60" s="15">
-        <f t="shared" si="26"/>
-        <v>256822.0135238095</v>
+        <f t="shared" si="28"/>
+        <v>260022.0135238095</v>
       </c>
       <c r="Y60" s="15">
-        <f t="shared" si="26"/>
-        <v>293491.30985714286</v>
+        <f t="shared" si="28"/>
+        <v>297091.30985714286</v>
       </c>
       <c r="Z60" s="15">
-        <f t="shared" si="26"/>
-        <v>308187.3919047619</v>
+        <f t="shared" si="28"/>
+        <v>311787.3919047619</v>
       </c>
       <c r="AA60" s="15">
-        <f t="shared" si="26"/>
-        <v>329856.68823809526</v>
+        <f t="shared" si="28"/>
+        <v>333856.68823809526</v>
       </c>
       <c r="AB60" s="15">
-        <f t="shared" si="26"/>
-        <v>351525.98457142862</v>
+        <f t="shared" si="28"/>
+        <v>355925.98457142862</v>
       </c>
       <c r="AC60" s="15">
-        <f t="shared" si="26"/>
-        <v>384251.24390476197</v>
+        <f t="shared" si="28"/>
+        <v>388651.24390476197</v>
       </c>
       <c r="AD60" s="15">
-        <f t="shared" si="26"/>
-        <v>416376.50323809532</v>
+        <f t="shared" si="28"/>
+        <v>420776.50323809532</v>
       </c>
       <c r="AE60" s="15">
-        <f t="shared" si="26"/>
-        <v>449101.76257142867</v>
+        <f t="shared" si="28"/>
+        <v>453501.76257142867</v>
       </c>
       <c r="AF60" s="15">
-        <f t="shared" si="26"/>
-        <v>481827.02190476202</v>
+        <f t="shared" si="28"/>
+        <v>486227.02190476202</v>
       </c>
       <c r="AG60" s="15">
-        <f t="shared" si="26"/>
-        <v>514552.28123809537</v>
+        <f t="shared" si="28"/>
+        <v>518952.28123809537</v>
       </c>
       <c r="AH60" s="15">
-        <f t="shared" si="26"/>
-        <v>547277.54057142872</v>
+        <f t="shared" si="28"/>
+        <v>551677.54057142872</v>
       </c>
       <c r="AI60" s="15">
-        <f t="shared" si="26"/>
-        <v>580002.79990476207</v>
+        <f t="shared" si="28"/>
+        <v>584402.79990476207</v>
       </c>
       <c r="AJ60" s="15">
-        <f t="shared" si="26"/>
-        <v>612728.05923809542</v>
+        <f t="shared" si="28"/>
+        <v>617128.05923809542</v>
       </c>
       <c r="AK60" s="15">
-        <f t="shared" si="26"/>
-        <v>645453.31857142877</v>
+        <f t="shared" si="28"/>
+        <v>649853.31857142877</v>
       </c>
       <c r="AL60" s="15">
-        <f t="shared" si="26"/>
-        <v>664932.1493333336</v>
+        <f t="shared" si="28"/>
+        <v>669332.1493333336</v>
       </c>
       <c r="AM60" s="15">
-        <f t="shared" si="26"/>
-        <v>697657.40866666695</v>
+        <f t="shared" si="28"/>
+        <v>702057.40866666695</v>
       </c>
       <c r="AN60" s="15">
-        <f t="shared" si="26"/>
-        <v>730382.6680000003</v>
+        <f t="shared" si="28"/>
+        <v>734782.6680000003</v>
       </c>
       <c r="AQ60" s="55"/>
     </row>
     <row r="61" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -12568,7 +12663,7 @@
     </row>
     <row r="62" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B62" s="16">
         <f>SUM(E62:P62)</f>
@@ -12691,10 +12786,10 @@
         <v>0</v>
       </c>
       <c r="AO62" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AP62" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AQ62" s="55">
         <f>TVA!$C$38</f>
@@ -12703,7 +12798,7 @@
     </row>
     <row r="63" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B63" s="16">
         <f>SUM(E63:P63)</f>
@@ -12829,7 +12924,7 @@
         <v>82</v>
       </c>
       <c r="AP63" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AQ63" s="55">
         <f>TVA!$C$38</f>
@@ -12838,7 +12933,7 @@
     </row>
     <row r="64" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B64" s="16">
         <f>SUM(E64:P64)</f>
@@ -12853,154 +12948,154 @@
         <v>10000</v>
       </c>
       <c r="E64" s="16">
-        <f t="shared" ref="E64:AN64" si="27">E62+E63</f>
+        <f t="shared" ref="E64:AN64" si="29">E62+E63</f>
         <v>18000</v>
       </c>
       <c r="F64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="G64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="I64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="J64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="K64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="O64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="P64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Q64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5000</v>
       </c>
       <c r="R64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="S64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="U64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="W64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AA64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AB64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>10000</v>
       </c>
       <c r="AD64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AE64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AH64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AI64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AJ64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AL64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AM64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AN64" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AQ64" s="55"/>
     </row>
     <row r="65" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -13047,7 +13142,7 @@
     </row>
     <row r="66" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B66" s="16">
         <f>SUM(E66:P66)</f>
@@ -13209,7 +13304,7 @@
     </row>
     <row r="67" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B67" s="16">
         <f>SUM(E67:P67)</f>
@@ -13217,7 +13312,7 @@
       </c>
       <c r="C67" s="16">
         <f>SUM(Q67:AB67)</f>
-        <v>176038.25</v>
+        <v>175598.25</v>
       </c>
       <c r="D67" s="16">
         <f>SUM(AC67:AN67)</f>
@@ -13273,39 +13368,39 @@
       </c>
       <c r="Q67" s="15">
         <f>Q8*TVA!$C$26+Q9*TVA!$D$26+Q10*TVA!$E$26+Q12*TVA!$F$26+Q28*TVA!$C$14+Q29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="R67" s="15">
         <f>R8*TVA!$C$26+R9*TVA!$D$26+R10*TVA!$E$26+R12*TVA!$F$26+R28*TVA!$C$14+R29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="S67" s="15">
         <f>S8*TVA!$C$26+S9*TVA!$D$26+S10*TVA!$E$26+S12*TVA!$F$26+S28*TVA!$C$14+S29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="T67" s="15">
         <f>T8*TVA!$C$26+T9*TVA!$D$26+T10*TVA!$E$26+T12*TVA!$F$26+T28*TVA!$C$14+T29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="U67" s="15">
         <f>U8*TVA!$C$26+U9*TVA!$D$26+U10*TVA!$E$26+U12*TVA!$F$26+U28*TVA!$C$14+U29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="V67" s="15">
         <f>V8*TVA!$C$26+V9*TVA!$D$26+V10*TVA!$E$26+V12*TVA!$F$26+V28*TVA!$C$14+V29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="W67" s="15">
         <f>W8*TVA!$C$26+W9*TVA!$D$26+W10*TVA!$E$26+W12*TVA!$F$26+W28*TVA!$C$14+W29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="X67" s="15">
         <f>X8*TVA!$C$26+X9*TVA!$D$26+X10*TVA!$E$26+X12*TVA!$F$26+X28*TVA!$C$14+X29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="Y67" s="15">
         <f>Y8*TVA!$C$26+Y9*TVA!$D$26+Y10*TVA!$E$26+Y12*TVA!$F$26+Y28*TVA!$C$14+Y29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="Z67" s="15">
         <f>Z8*TVA!$C$26+Z9*TVA!$D$26+Z10*TVA!$E$26+Z12*TVA!$F$26+Z28*TVA!$C$14+Z29*$AQ$29</f>
@@ -13313,11 +13408,11 @@
       </c>
       <c r="AA67" s="15">
         <f>AA8*TVA!$C$26+AA9*TVA!$D$26+AA10*TVA!$E$26+AA12*TVA!$F$26+AA28*TVA!$C$14+AA29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="AB67" s="15">
         <f>AB8*TVA!$C$26+AB9*TVA!$D$26+AB10*TVA!$E$26+AB12*TVA!$F$26+AB28*TVA!$C$14+AB29*$AQ$29</f>
-        <v>15011.464285714283</v>
+        <v>14971.464285714283</v>
       </c>
       <c r="AC67" s="15">
         <f>AC8*TVA!$C$26+AC9*TVA!$D$26+AC10*TVA!$E$26+AC12*TVA!$F$26+AC28*TVA!$C$14+AC29*$AQ$29</f>
@@ -13371,7 +13466,7 @@
     </row>
     <row r="68" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B68" s="16">
         <f>SUM(E68:P68)</f>
@@ -13386,154 +13481,154 @@
         <v>24473.000000000004</v>
       </c>
       <c r="E68" s="15">
-        <f t="shared" ref="E68:AN68" si="28">SUMPRODUCT(E39:E55,$AQ$39:$AQ$55)</f>
+        <f t="shared" ref="E68:AN68" si="30">SUMPRODUCT(E39:E55,$AQ$39:$AQ$55)</f>
         <v>451</v>
       </c>
       <c r="F68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>691</v>
       </c>
       <c r="G68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>399.5</v>
       </c>
       <c r="H68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1399.5</v>
       </c>
       <c r="I68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3959.5</v>
       </c>
       <c r="J68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>359.5</v>
       </c>
       <c r="K68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>159.5</v>
       </c>
       <c r="L68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>159.5</v>
       </c>
       <c r="M68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>159.5</v>
       </c>
       <c r="N68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1151</v>
       </c>
       <c r="O68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1159.5</v>
       </c>
       <c r="P68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1159.5</v>
       </c>
       <c r="Q68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="R68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="S68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="T68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="U68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="V68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="W68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="X68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="Y68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>768.16666666666674</v>
       </c>
       <c r="Z68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2242.666666666667</v>
       </c>
       <c r="AA68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2268.166666666667</v>
       </c>
       <c r="AB68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2268.166666666667</v>
       </c>
       <c r="AC68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AD68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AE68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AF68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AG68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AH68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AI68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AJ68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AK68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AL68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1992.6666666666667</v>
       </c>
       <c r="AM68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AN68" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2043.6666666666667</v>
       </c>
       <c r="AQ68" s="55"/>
     </row>
     <row r="69" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B69" s="16">
         <f>SUM(E69:P69)</f>
@@ -13548,154 +13643,154 @@
         <v>2000</v>
       </c>
       <c r="E69" s="15">
-        <f t="shared" ref="E69:AN69" si="29">E62*$AQ$62+E63*$AQ$63</f>
+        <f t="shared" ref="E69:AN69" si="31">E62*$AQ$62+E63*$AQ$63</f>
         <v>3600</v>
       </c>
       <c r="F69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="I69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="O69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="P69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="Q69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1000</v>
       </c>
       <c r="R69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="T69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="V69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="W69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="X69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="Y69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="Z69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AA69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AB69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>2000</v>
       </c>
       <c r="AD69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AF69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AG69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AH69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AI69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AJ69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AK69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AL69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AM69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AN69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AQ69" s="55"/>
     </row>
     <row r="70" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B70" s="16">
         <f>SUM(E70:P70)</f>
@@ -13703,308 +13798,308 @@
       </c>
       <c r="C70" s="16">
         <f>SUM(Q70:AB70)</f>
-        <v>57519.250000000015</v>
+        <v>57959.250000000015</v>
       </c>
       <c r="D70" s="16">
         <f>SUM(AC70:AN70)</f>
         <v>117180.50000000001</v>
       </c>
       <c r="E70" s="15">
-        <f t="shared" ref="E70:AN70" si="30">E66-E67-E68-E69</f>
+        <f t="shared" ref="E70:AN70" si="32">E66-E67-E68-E69</f>
         <v>-4051</v>
       </c>
       <c r="F70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-691</v>
       </c>
       <c r="G70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-238.35714285714312</v>
       </c>
       <c r="H70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-975.25</v>
       </c>
       <c r="I70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-3739.5</v>
       </c>
       <c r="J70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>457.57142857142844</v>
       </c>
       <c r="K70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>871.6785714285711</v>
       </c>
       <c r="L70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>576.42857142857156</v>
       </c>
       <c r="M70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>141.642857142857</v>
       </c>
       <c r="N70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-1151</v>
       </c>
       <c r="O70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>387.60714285714312</v>
       </c>
       <c r="P70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>92.357142857142662</v>
       </c>
       <c r="Q70" s="15">
-        <f t="shared" si="30"/>
-        <v>4327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>4367.5119047619055</v>
       </c>
       <c r="R70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="S70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="T70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="U70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="V70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="W70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="X70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="Y70" s="15">
-        <f t="shared" si="30"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="Z70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>2916.6190476190468</v>
       </c>
       <c r="AA70" s="15">
-        <f t="shared" si="30"/>
-        <v>3827.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>3867.5119047619055</v>
       </c>
       <c r="AB70" s="15">
-        <f t="shared" si="30"/>
-        <v>3827.5119047619055</v>
+        <f t="shared" si="32"/>
+        <v>3867.5119047619055</v>
       </c>
       <c r="AC70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8077.6904761904789</v>
       </c>
       <c r="AD70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AE70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AF70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AG70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AH70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AI70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AJ70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AK70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AL70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8325.9047619047615</v>
       </c>
       <c r="AM70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AN70" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>10077.690476190479</v>
       </c>
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E71" s="15">
         <v>0</v>
       </c>
       <c r="F71" s="15">
-        <f t="shared" ref="F71:AN71" si="31">E73</f>
+        <f t="shared" ref="F71:AN71" si="33">E73</f>
         <v>4051</v>
       </c>
       <c r="G71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>4742</v>
       </c>
       <c r="H71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>4980.3571428571431</v>
       </c>
       <c r="I71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>5955.6071428571431</v>
       </c>
       <c r="J71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>9695.1071428571431</v>
       </c>
       <c r="K71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>9237.5357142857138</v>
       </c>
       <c r="L71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8365.8571428571431</v>
       </c>
       <c r="M71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>7789.4285714285716</v>
       </c>
       <c r="N71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>7647.7857142857147</v>
       </c>
       <c r="O71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8798.7857142857138</v>
       </c>
       <c r="P71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8411.1785714285706</v>
       </c>
       <c r="Q71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8318.8214285714275</v>
       </c>
       <c r="R71" s="15">
-        <f t="shared" si="31"/>
-        <v>3991.309523809522</v>
+        <f t="shared" si="33"/>
+        <v>3951.309523809522</v>
       </c>
       <c r="S71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="T71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="U71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="V71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="W71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="X71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Y71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Z71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AA71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AB71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AC71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AF71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AH71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AI71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AJ71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AK71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AL71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AM71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AN71" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B72" s="16">
         <f>SUM(E72:P72)</f>
@@ -14012,160 +14107,160 @@
       </c>
       <c r="C72" s="16">
         <f>SUM(Q72:AB72)</f>
-        <v>49200.428571428587</v>
+        <v>49640.428571428587</v>
       </c>
       <c r="D72" s="16">
         <f>SUM(AC72:AN72)</f>
         <v>117180.50000000001</v>
       </c>
       <c r="E72" s="15">
-        <f t="shared" ref="E72:AN72" si="32">MAX(0,E70-E71)</f>
+        <f t="shared" ref="E72:AN72" si="34">MAX(0,E70-E71)</f>
         <v>0</v>
       </c>
       <c r="F72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="G72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="H72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="I72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="P72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="R72" s="15">
-        <f t="shared" si="32"/>
-        <v>1336.2023809523835</v>
+        <f t="shared" si="34"/>
+        <v>1416.2023809523835</v>
       </c>
       <c r="S72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="T72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="U72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="V72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="W72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="X72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="Y72" s="15">
-        <f t="shared" si="32"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="Z72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2916.6190476190468</v>
       </c>
       <c r="AA72" s="15">
-        <f t="shared" si="32"/>
-        <v>3827.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>3867.5119047619055</v>
       </c>
       <c r="AB72" s="15">
-        <f t="shared" si="32"/>
-        <v>3827.5119047619055</v>
+        <f t="shared" si="34"/>
+        <v>3867.5119047619055</v>
       </c>
       <c r="AC72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>8077.6904761904789</v>
       </c>
       <c r="AD72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AE72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AF72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AG72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AH72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AI72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AJ72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AK72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AL72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>8325.9047619047615</v>
       </c>
       <c r="AM72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AN72" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10077.690476190479</v>
       </c>
     </row>
     <row r="73" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B73" s="16">
         <f>P73</f>
@@ -14180,153 +14275,153 @@
         <v>0</v>
       </c>
       <c r="E73" s="15">
-        <f t="shared" ref="E73:AN73" si="33">MAX(0,E71-E70)</f>
+        <f t="shared" ref="E73:AN73" si="35">MAX(0,E71-E70)</f>
         <v>4051</v>
       </c>
       <c r="F73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>4742</v>
       </c>
       <c r="G73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>4980.3571428571431</v>
       </c>
       <c r="H73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>5955.6071428571431</v>
       </c>
       <c r="I73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9695.1071428571431</v>
       </c>
       <c r="J73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9237.5357142857138</v>
       </c>
       <c r="K73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8365.8571428571431</v>
       </c>
       <c r="L73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7789.4285714285716</v>
       </c>
       <c r="M73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7647.7857142857147</v>
       </c>
       <c r="N73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8798.7857142857138</v>
       </c>
       <c r="O73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8411.1785714285706</v>
       </c>
       <c r="P73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8318.8214285714275</v>
       </c>
       <c r="Q73" s="15">
-        <f t="shared" si="33"/>
-        <v>3991.309523809522</v>
+        <f t="shared" si="35"/>
+        <v>3951.309523809522</v>
       </c>
       <c r="R73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="S73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="U73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="V73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="W73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="X73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Z73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AA73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AB73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AC73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AD73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AE73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AF73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AH73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AK73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AL73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AM73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AN73" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B74" s="16">
         <f>SUM(E74:P74)</f>
@@ -14334,159 +14429,159 @@
       </c>
       <c r="C74" s="16">
         <f>SUM(Q74:AB74)</f>
-        <v>45372.916666666679</v>
+        <v>45772.916666666679</v>
       </c>
       <c r="D74" s="16">
         <f>SUM(AC74:AN74)</f>
-        <v>110930.32142857145</v>
+        <v>110970.32142857145</v>
       </c>
       <c r="E74" s="15">
         <v>0</v>
       </c>
       <c r="F74" s="15">
-        <f t="shared" ref="F74:AN74" si="34">E72</f>
+        <f t="shared" ref="F74:AN74" si="36">E72</f>
         <v>0</v>
       </c>
       <c r="G74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="I74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="J74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="K74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="P74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Q74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="S74" s="15">
-        <f t="shared" si="34"/>
-        <v>1336.2023809523835</v>
+        <f t="shared" si="36"/>
+        <v>1416.2023809523835</v>
       </c>
       <c r="T74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="U74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="V74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="W74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="X74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="Y74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="Z74" s="15">
-        <f t="shared" si="34"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="AA74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>2916.6190476190468</v>
       </c>
       <c r="AB74" s="15">
-        <f t="shared" si="34"/>
-        <v>3827.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>3867.5119047619055</v>
       </c>
       <c r="AC74" s="15">
-        <f t="shared" si="34"/>
-        <v>3827.5119047619055</v>
+        <f t="shared" si="36"/>
+        <v>3867.5119047619055</v>
       </c>
       <c r="AD74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8077.6904761904789</v>
       </c>
       <c r="AE74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AF74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AG74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AH74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AI74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AJ74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AK74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AL74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
       <c r="AM74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8325.9047619047615</v>
       </c>
       <c r="AN74" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>10077.690476190479</v>
       </c>
     </row>
     <row r="75" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B75" s="16">
         <f>SUM(E75:P75)</f>
@@ -14494,160 +14589,160 @@
       </c>
       <c r="C75" s="16">
         <f>SUM(Q75:AB75)</f>
-        <v>12146.333333333332</v>
+        <v>12186.333333333332</v>
       </c>
       <c r="D75" s="16">
         <f>SUM(AC75:AN75)</f>
-        <v>6250.1785714285734</v>
+        <v>6210.1785714285734</v>
       </c>
       <c r="E75" s="16">
-        <f t="shared" ref="E75:AN75" si="35">E66-E67-E68-E69-E74</f>
+        <f t="shared" ref="E75:AN75" si="37">E66-E67-E68-E69-E74</f>
         <v>-4051</v>
       </c>
       <c r="F75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-691</v>
       </c>
       <c r="G75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-238.35714285714312</v>
       </c>
       <c r="H75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-975.25</v>
       </c>
       <c r="I75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-3739.5</v>
       </c>
       <c r="J75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>457.57142857142844</v>
       </c>
       <c r="K75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>871.6785714285711</v>
       </c>
       <c r="L75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>576.42857142857156</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>141.642857142857</v>
       </c>
       <c r="N75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1151</v>
       </c>
       <c r="O75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>387.60714285714312</v>
       </c>
       <c r="P75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>92.357142857142662</v>
       </c>
       <c r="Q75" s="16">
-        <f t="shared" si="35"/>
-        <v>4327.5119047619055</v>
+        <f t="shared" si="37"/>
+        <v>4367.5119047619055</v>
       </c>
       <c r="R75" s="16">
-        <f t="shared" si="35"/>
-        <v>5327.5119047619055</v>
+        <f t="shared" si="37"/>
+        <v>5367.5119047619055</v>
       </c>
       <c r="S75" s="16">
-        <f t="shared" si="35"/>
-        <v>3991.309523809522</v>
+        <f t="shared" si="37"/>
+        <v>3951.309523809522</v>
       </c>
       <c r="T75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="U75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="V75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="W75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="X75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Y75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Z75" s="16">
-        <f t="shared" si="35"/>
-        <v>-2410.8928571428587</v>
+        <f t="shared" si="37"/>
+        <v>-2450.8928571428587</v>
       </c>
       <c r="AA75" s="16">
-        <f t="shared" si="35"/>
-        <v>910.8928571428587</v>
+        <f t="shared" si="37"/>
+        <v>950.8928571428587</v>
       </c>
       <c r="AB75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AC75" s="16">
-        <f t="shared" si="35"/>
-        <v>4250.1785714285734</v>
+        <f t="shared" si="37"/>
+        <v>4210.1785714285734</v>
       </c>
       <c r="AD75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>2000</v>
       </c>
       <c r="AE75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AF75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AH75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AI75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AJ75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AL75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1751.7857142857174</v>
       </c>
       <c r="AM75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>1751.7857142857174</v>
       </c>
       <c r="AN75" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
@@ -14694,7 +14789,7 @@
     </row>
     <row r="77" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B77" s="16">
         <f>SUM(E77:P77)</f>
@@ -14855,14 +14950,15 @@
         <v>82</v>
       </c>
       <c r="AP77" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>336</v>
+        <v>457</v>
       </c>
       <c r="B78" s="16">
+        <f>SUM(E78:P78)</f>
         <v>70000</v>
       </c>
       <c r="C78" s="16">
@@ -14985,12 +15081,12 @@
         <v>82</v>
       </c>
       <c r="AP78" s="1" t="s">
-        <v>337</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B79" s="16">
         <f>SUM(E79:P79)</f>
@@ -14998,163 +15094,163 @@
       </c>
       <c r="C79" s="16">
         <f>SUM(Q79:AB79)</f>
-        <v>441904.67504761915</v>
+        <v>446344.67504761915</v>
       </c>
       <c r="D79" s="16">
         <f>SUM(AC79:AN79)</f>
-        <v>375106.86200000008</v>
+        <v>375066.86200000008</v>
       </c>
       <c r="E79" s="15">
-        <f t="shared" ref="E79:AN79" si="36">E59-E64+E75+E77+E78</f>
+        <f t="shared" ref="E79:AN79" si="38">E59-E64+E75+E77+E78</f>
         <v>45237</v>
       </c>
       <c r="F79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6248.9999999999982</v>
       </c>
       <c r="G79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>8497.3571428571413</v>
       </c>
       <c r="H79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-10979.000000000002</v>
       </c>
       <c r="I79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-38933.25</v>
       </c>
       <c r="J79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>14289.714285714283</v>
       </c>
       <c r="K79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>1719.3571428571395</v>
       </c>
       <c r="L79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2579.1071428571381</v>
       </c>
       <c r="M79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-9922.6428571428569</v>
       </c>
       <c r="N79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>8589</v>
       </c>
       <c r="O79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-4568.2857142857174</v>
       </c>
       <c r="P79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>31691.464285714283</v>
       </c>
       <c r="Q79" s="15">
-        <f t="shared" si="36"/>
-        <v>35996.80823809524</v>
+        <f t="shared" si="38"/>
+        <v>36436.80823809524</v>
       </c>
       <c r="R79" s="15">
-        <f t="shared" si="36"/>
-        <v>41696.80823809524</v>
+        <f t="shared" si="38"/>
+        <v>42136.80823809524</v>
       </c>
       <c r="S79" s="15">
-        <f t="shared" si="36"/>
-        <v>40660.605857142851</v>
+        <f t="shared" si="38"/>
+        <v>41020.605857142851</v>
       </c>
       <c r="T79" s="15">
-        <f t="shared" si="36"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="38"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="U79" s="15">
-        <f t="shared" si="36"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="38"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="V79" s="15">
-        <f t="shared" si="36"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="38"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="W79" s="15">
-        <f t="shared" si="36"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="38"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="X79" s="15">
-        <f t="shared" si="36"/>
-        <v>36669.296333333332</v>
+        <f t="shared" si="38"/>
+        <v>37069.296333333332</v>
       </c>
       <c r="Y79" s="15">
-        <f t="shared" si="36"/>
-        <v>-10330.703666666668</v>
+        <f t="shared" si="38"/>
+        <v>-9930.7036666666681</v>
       </c>
       <c r="Z79" s="15">
-        <f t="shared" si="36"/>
-        <v>59285.189190476187</v>
+        <f t="shared" si="38"/>
+        <v>59245.189190476187</v>
       </c>
       <c r="AA79" s="15">
-        <f t="shared" si="36"/>
-        <v>22580.189190476194</v>
+        <f t="shared" si="38"/>
+        <v>23020.189190476194</v>
       </c>
       <c r="AB79" s="15">
-        <f t="shared" si="36"/>
-        <v>68669.296333333332</v>
+        <f t="shared" si="38"/>
+        <v>69069.296333333332</v>
       </c>
       <c r="AC79" s="15">
-        <f t="shared" si="36"/>
-        <v>26975.437904761908</v>
+        <f t="shared" si="38"/>
+        <v>26935.437904761908</v>
       </c>
       <c r="AD79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>34125.259333333335</v>
       </c>
       <c r="AE79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AF79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AG79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AH79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AI79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AJ79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AK79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-61274.740666666665</v>
       </c>
       <c r="AL79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>111727.04504761906</v>
       </c>
       <c r="AM79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>34477.045047619053</v>
       </c>
       <c r="AN79" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>32725.259333333335</v>
       </c>
       <c r="AP79" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B80" s="16">
         <f>P80</f>
@@ -15162,160 +15258,160 @@
       </c>
       <c r="C80" s="16">
         <f>AB80</f>
-        <v>496353.49647619051</v>
+        <v>500793.49647619051</v>
       </c>
       <c r="D80" s="16">
         <f>AN80</f>
-        <v>871460.35847619059</v>
+        <v>875860.35847619059</v>
       </c>
       <c r="E80" s="16">
         <f>E79</f>
         <v>45237</v>
       </c>
       <c r="F80" s="16">
-        <f t="shared" ref="F80:AN80" si="37">E80+F79</f>
+        <f t="shared" ref="F80:AN80" si="39">E80+F79</f>
         <v>51486</v>
       </c>
       <c r="G80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>59983.357142857145</v>
       </c>
       <c r="H80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>49004.357142857145</v>
       </c>
       <c r="I80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>10071.107142857145</v>
       </c>
       <c r="J80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>24360.821428571428</v>
       </c>
       <c r="K80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>26080.178571428565</v>
       </c>
       <c r="L80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>28659.285714285703</v>
       </c>
       <c r="M80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>18736.642857142848</v>
       </c>
       <c r="N80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>27325.642857142848</v>
       </c>
       <c r="O80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>22757.35714285713</v>
       </c>
       <c r="P80" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>54448.821428571413</v>
       </c>
       <c r="Q80" s="16">
-        <f t="shared" si="37"/>
-        <v>90445.629666666646</v>
+        <f t="shared" si="39"/>
+        <v>90885.629666666646</v>
       </c>
       <c r="R80" s="16">
-        <f t="shared" si="37"/>
-        <v>132142.43790476187</v>
+        <f t="shared" si="39"/>
+        <v>133022.43790476187</v>
       </c>
       <c r="S80" s="16">
-        <f t="shared" si="37"/>
-        <v>172803.04376190473</v>
+        <f t="shared" si="39"/>
+        <v>174043.04376190473</v>
       </c>
       <c r="T80" s="16">
-        <f t="shared" si="37"/>
-        <v>209472.34009523806</v>
+        <f t="shared" si="39"/>
+        <v>211112.34009523806</v>
       </c>
       <c r="U80" s="16">
-        <f t="shared" si="37"/>
-        <v>246141.63642857139</v>
+        <f t="shared" si="39"/>
+        <v>248181.63642857139</v>
       </c>
       <c r="V80" s="16">
-        <f t="shared" si="37"/>
-        <v>282810.93276190473</v>
+        <f t="shared" si="39"/>
+        <v>285250.93276190473</v>
       </c>
       <c r="W80" s="16">
-        <f t="shared" si="37"/>
-        <v>319480.22909523803</v>
+        <f t="shared" si="39"/>
+        <v>322320.22909523803</v>
       </c>
       <c r="X80" s="16">
-        <f t="shared" si="37"/>
-        <v>356149.52542857139</v>
+        <f t="shared" si="39"/>
+        <v>359389.52542857139</v>
       </c>
       <c r="Y80" s="16">
-        <f t="shared" si="37"/>
-        <v>345818.82176190475</v>
+        <f t="shared" si="39"/>
+        <v>349458.82176190475</v>
       </c>
       <c r="Z80" s="16">
-        <f t="shared" si="37"/>
-        <v>405104.01095238095</v>
+        <f t="shared" si="39"/>
+        <v>408704.01095238095</v>
       </c>
       <c r="AA80" s="16">
-        <f t="shared" si="37"/>
-        <v>427684.20014285715</v>
+        <f t="shared" si="39"/>
+        <v>431724.20014285715</v>
       </c>
       <c r="AB80" s="16">
-        <f t="shared" si="37"/>
-        <v>496353.49647619051</v>
+        <f t="shared" si="39"/>
+        <v>500793.49647619051</v>
       </c>
       <c r="AC80" s="16">
-        <f t="shared" si="37"/>
-        <v>523328.93438095244</v>
+        <f t="shared" si="39"/>
+        <v>527728.93438095239</v>
       </c>
       <c r="AD80" s="16">
-        <f t="shared" si="37"/>
-        <v>557454.19371428574</v>
+        <f t="shared" si="39"/>
+        <v>561854.19371428574</v>
       </c>
       <c r="AE80" s="16">
-        <f t="shared" si="37"/>
-        <v>590179.45304761908</v>
+        <f t="shared" si="39"/>
+        <v>594579.45304761908</v>
       </c>
       <c r="AF80" s="16">
-        <f t="shared" si="37"/>
-        <v>622904.71238095243</v>
+        <f t="shared" si="39"/>
+        <v>627304.71238095243</v>
       </c>
       <c r="AG80" s="16">
-        <f t="shared" si="37"/>
-        <v>655629.97171428578</v>
+        <f t="shared" si="39"/>
+        <v>660029.97171428578</v>
       </c>
       <c r="AH80" s="16">
-        <f t="shared" si="37"/>
-        <v>688355.23104761913</v>
+        <f t="shared" si="39"/>
+        <v>692755.23104761913</v>
       </c>
       <c r="AI80" s="16">
-        <f t="shared" si="37"/>
-        <v>721080.49038095248</v>
+        <f t="shared" si="39"/>
+        <v>725480.49038095248</v>
       </c>
       <c r="AJ80" s="16">
-        <f t="shared" si="37"/>
-        <v>753805.74971428583</v>
+        <f t="shared" si="39"/>
+        <v>758205.74971428583</v>
       </c>
       <c r="AK80" s="16">
-        <f t="shared" si="37"/>
-        <v>692531.00904761918</v>
+        <f t="shared" si="39"/>
+        <v>696931.00904761918</v>
       </c>
       <c r="AL80" s="16">
-        <f t="shared" si="37"/>
-        <v>804258.05409523821</v>
+        <f t="shared" si="39"/>
+        <v>808658.05409523821</v>
       </c>
       <c r="AM80" s="16">
-        <f t="shared" si="37"/>
-        <v>838735.09914285725</v>
+        <f t="shared" si="39"/>
+        <v>843135.09914285725</v>
       </c>
       <c r="AN80" s="16">
-        <f t="shared" si="37"/>
-        <v>871460.35847619059</v>
+        <f t="shared" si="39"/>
+        <v>875860.35847619059</v>
       </c>
     </row>
     <row r="82" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
@@ -15362,235 +15458,235 @@
     </row>
     <row r="83" spans="1:43" ht="26" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B84" s="14">
         <v>300</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B85" s="14">
         <v>700</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B86" s="14">
         <v>15000</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B87" s="14">
         <v>15000</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>351</v>
+        <v>464</v>
       </c>
     </row>
     <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B88" s="11">
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B89" s="41">
         <v>0.02</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B90" s="71">
         <v>40</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="B91" s="71">
         <v>300</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
     </row>
     <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="B92" s="71">
         <v>80</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
     </row>
     <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="B93" s="71">
         <v>50</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
     </row>
     <row r="95" spans="1:43" ht="26" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>356</v>
+        <v>459</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C96" s="52">
         <f>EDATE($B$3,2)</f>
         <v>46388</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C97" s="52">
         <f>EDATE($B$3,12)</f>
         <v>46692</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>471</v>
+        <v>353</v>
       </c>
       <c r="C98" s="52">
         <f>EDATE($B$3,12)</f>
         <v>46692</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>472</v>
+        <v>356</v>
       </c>
       <c r="C99" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C100" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C101" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -15612,91 +15708,91 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B10" s="1">
         <v>19</v>
@@ -15708,12 +15804,12 @@
         <v>82</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B11" s="1">
         <v>22</v>
@@ -15725,15 +15821,15 @@
         <v>82</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C12" s="41">
         <v>5.5E-2</v>
@@ -15742,15 +15838,15 @@
         <v>82</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C13" s="41">
         <v>0.2</v>
@@ -15759,15 +15855,15 @@
         <v>82</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" s="41">
         <v>0.2</v>
@@ -15776,12 +15872,12 @@
         <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B15" s="1">
         <v>27</v>
@@ -15810,12 +15906,12 @@
         <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B17" s="1">
         <v>29</v>
@@ -15835,7 +15931,7 @@
         <v>67</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C18" s="41">
         <v>0</v>
@@ -15844,15 +15940,15 @@
         <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C19" s="41">
         <v>0.2</v>
@@ -15866,7 +15962,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B20" s="1">
         <v>33</v>
@@ -15878,30 +15974,30 @@
         <v>82</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="26" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C23" s="15">
         <f>'Prix et marges'!C17</f>
@@ -15922,7 +16018,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C24" s="50">
         <f>'Prix et marges'!C12</f>
@@ -15943,7 +16039,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C25" s="15">
         <f>C23*C24</f>
@@ -15964,7 +16060,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C26" s="15">
         <f>'Prix et marges'!C19*$C$10+'Prix et marges'!C22*$C$11+'Prix et marges'!C9*'Prix et marges'!C23*$C$12+'Prix et marges'!C9*'Prix et marges'!C24*$C$13+'Prix et marges'!C26*$C$14+'Prix et marges'!C27*$C$15+'Prix et marges'!C28*$C$16+'Prix et marges'!C29*$C$17+'Prix et marges'!C30*'Prix et marges'!C17*$C$18+'Prix et marges'!C31*'Prix et marges'!C17*$C$19+'Prix et marges'!C33*$C$20</f>
@@ -15985,7 +16081,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C27" s="15">
         <f>C25-C26</f>
@@ -16006,27 +16102,27 @@
     </row>
     <row r="29" spans="1:6" ht="26" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C30" s="41">
         <v>0.2</v>
@@ -16040,10 +16136,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C31" s="41">
         <v>0.2</v>
@@ -16057,10 +16153,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C32" s="41">
         <v>0.2</v>
@@ -16069,15 +16165,15 @@
         <v>82</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C33" s="41">
         <v>0</v>
@@ -16086,15 +16182,15 @@
         <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C34" s="41">
         <v>0.2</v>
@@ -16108,10 +16204,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C35" s="41">
         <v>0</v>
@@ -16120,15 +16216,15 @@
         <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C36" s="41">
         <v>0.1</v>
@@ -16137,15 +16233,15 @@
         <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C37" s="41">
         <v>0</v>
@@ -16154,15 +16250,15 @@
         <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C38" s="41">
         <v>0.2</v>
@@ -16176,7 +16272,7 @@
     </row>
     <row r="40" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="60" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B40"/>
       <c r="C40"/>
@@ -16530,20 +16626,20 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="31">
         <f>'Budget 36 mois'!E5</f>
@@ -16596,7 +16692,7 @@
     </row>
     <row r="6" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -16614,7 +16710,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B7" s="12">
         <f>SUM(C7:N7)</f>
@@ -16671,7 +16767,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" s="12">
         <f>SUM(C8:N8)</f>
@@ -16692,7 +16788,7 @@
     </row>
     <row r="9" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B9" s="13">
         <f>SUM(C9:N9)</f>
@@ -16749,7 +16845,7 @@
     </row>
     <row r="11" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -16767,7 +16863,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B12" s="15">
         <f>SUM(C12:N12)</f>
@@ -16824,7 +16920,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(C13:N13)</f>
@@ -16845,7 +16941,7 @@
     </row>
     <row r="14" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B14" s="16">
         <f>SUM(C14:N14)</f>
@@ -16902,7 +16998,7 @@
     </row>
     <row r="16" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -16920,7 +17016,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" s="15">
         <f>SUM(C17:N17)</f>
@@ -16977,7 +17073,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="15">
         <f>SUM(C18:N18)</f>
@@ -16998,7 +17094,7 @@
     </row>
     <row r="19" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" s="16">
         <f>SUM(C19:N19)</f>
@@ -17055,7 +17151,7 @@
     </row>
     <row r="21" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -17073,7 +17169,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B22" s="15">
         <f>SUM(C22:N22)</f>
@@ -17130,7 +17226,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B23" s="15">
         <f>SUM(C23:N23)</f>
@@ -17151,7 +17247,7 @@
     </row>
     <row r="24" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B24" s="16">
         <f>SUM(C24:N24)</f>
@@ -17208,7 +17304,7 @@
     </row>
     <row r="26" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -17226,7 +17322,7 @@
     </row>
     <row r="27" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -17259,7 +17355,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="59" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -17273,7 +17369,7 @@
     </row>
     <row r="2" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -17317,16 +17413,16 @@
         <v>27</v>
       </c>
       <c r="C5" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="62" t="s">
-        <v>128</v>
-      </c>
       <c r="F5" s="62" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -17335,7 +17431,7 @@
     </row>
     <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="37"/>
@@ -17349,10 +17445,10 @@
     </row>
     <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="B7" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C7" s="66">
         <f>'Budget 36 mois'!B7</f>
@@ -17367,7 +17463,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -17376,10 +17472,10 @@
     </row>
     <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C8" s="66">
         <f>'Budget 36 mois'!B11</f>
@@ -17394,7 +17490,7 @@
         <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -17403,10 +17499,10 @@
     </row>
     <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C9" s="66">
         <f>'Budget 36 mois'!B8</f>
@@ -17428,10 +17524,10 @@
     </row>
     <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B10" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C10" s="66">
         <f>'Budget 36 mois'!B9</f>
@@ -17453,10 +17549,10 @@
     </row>
     <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B11" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C11" s="66">
         <f>'Budget 36 mois'!B10</f>
@@ -17478,25 +17574,25 @@
     </row>
     <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C12" s="66">
         <f>'Budget 36 mois'!B12</f>
         <v>7</v>
       </c>
       <c r="D12" s="66">
-        <f>3*40</f>
+        <f>'Budget 36 mois'!C12</f>
         <v>120</v>
       </c>
       <c r="E12" s="66">
-        <f>6*40</f>
+        <f>'Budget 36 mois'!D12</f>
         <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
@@ -17505,10 +17601,10 @@
     </row>
     <row r="13" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C13" s="69">
         <f>'Budget 36 mois'!B13</f>
@@ -17530,7 +17626,7 @@
     </row>
     <row r="14" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B14" s="37"/>
       <c r="C14" s="37"/>
@@ -17544,7 +17640,7 @@
     </row>
     <row r="15" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>51</v>
@@ -17569,7 +17665,7 @@
     </row>
     <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
@@ -17580,7 +17676,7 @@
       </c>
       <c r="D16" s="64">
         <f>'Budget 36 mois'!C30</f>
-        <v>1444293.2142857141</v>
+        <v>1439893.2142857141</v>
       </c>
       <c r="E16" s="64">
         <f>'Budget 36 mois'!D30</f>
@@ -17605,7 +17701,7 @@
       </c>
       <c r="D17" s="36">
         <f>'Budget 36 mois'!C31</f>
-        <v>624456.7857142858</v>
+        <v>628856.7857142858</v>
       </c>
       <c r="E17" s="36">
         <f>'Budget 36 mois'!D31</f>
@@ -17625,7 +17721,7 @@
       </c>
       <c r="D18" s="67">
         <f>IF(D15&gt;0,D17/D15,0)</f>
-        <v>0.30185222270176965</v>
+        <v>0.30397911091929231</v>
       </c>
       <c r="E18" s="67">
         <f>IF(E15&gt;0,E17/E15,0)</f>
@@ -17634,7 +17730,7 @@
     </row>
     <row r="19" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -17652,7 +17748,7 @@
         <v>643836.88800000015</v>
       </c>
       <c r="F19" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -17661,7 +17757,7 @@
     </row>
     <row r="20" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
@@ -17686,7 +17782,7 @@
     </row>
     <row r="21" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B21" t="s">
         <v>51</v>
@@ -17704,7 +17800,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -17713,7 +17809,7 @@
     </row>
     <row r="22" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B22" t="s">
         <v>51</v>
@@ -17731,7 +17827,7 @@
         <v>29210.000000000004</v>
       </c>
       <c r="F22" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -17740,7 +17836,7 @@
     </row>
     <row r="23" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
@@ -17765,7 +17861,7 @@
     </row>
     <row r="24" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
@@ -17790,7 +17886,7 @@
     </row>
     <row r="25" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
@@ -17808,7 +17904,7 @@
         <v>76559.999999999971</v>
       </c>
       <c r="F25" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
@@ -17817,7 +17913,7 @@
     </row>
     <row r="26" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>51</v>
@@ -17842,7 +17938,7 @@
     </row>
     <row r="27" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>51</v>
@@ -17853,7 +17949,7 @@
       </c>
       <c r="D27" s="36">
         <f>'Budget 36 mois'!C59</f>
-        <v>387758.34171428578</v>
+        <v>392158.34171428578</v>
       </c>
       <c r="E27" s="36">
         <f>'Budget 36 mois'!D59</f>
@@ -17867,7 +17963,7 @@
     </row>
     <row r="28" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="37" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
@@ -17881,7 +17977,7 @@
     </row>
     <row r="29" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
@@ -17906,10 +18002,10 @@
     </row>
     <row r="30" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C30" s="64">
         <f>C27-C29</f>
@@ -17917,7 +18013,7 @@
       </c>
       <c r="D30" s="64">
         <f>D27-D29</f>
-        <v>382758.34171428578</v>
+        <v>387158.34171428578</v>
       </c>
       <c r="E30" s="64">
         <f>E27-E29</f>
@@ -17931,10 +18027,10 @@
     </row>
     <row r="31" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C31" s="36">
         <f>C30</f>
@@ -17942,11 +18038,11 @@
       </c>
       <c r="D31" s="36">
         <f>C31+D30</f>
-        <v>328525.98457142862</v>
+        <v>332925.98457142862</v>
       </c>
       <c r="E31" s="36">
         <f>D31+E30</f>
-        <v>697382.66800000018</v>
+        <v>701782.66800000018</v>
       </c>
       <c r="F31"/>
       <c r="G31"/>
@@ -17956,10 +18052,10 @@
     </row>
     <row r="32" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" s="68">
         <f>IF(C17&gt;0,C26/(C17/C13),0)</f>
@@ -17967,14 +18063,14 @@
       </c>
       <c r="D32" s="68">
         <f>IF(D17&gt;0,D26/(D17/D13),0)</f>
-        <v>57.994184322259507</v>
+        <v>57.588409244666757</v>
       </c>
       <c r="E32" s="68">
         <f>IF(E17&gt;0,E26/(E17/E13),0)</f>
         <v>212.59935743716258</v>
       </c>
       <c r="F32" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
@@ -17995,7 +18091,7 @@
     </row>
     <row r="34" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="37" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="37"/>
@@ -18009,10 +18105,10 @@
     </row>
     <row r="35" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="38" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C35" s="36">
         <f>MAX(0,-MIN(C31:E31))</f>
@@ -18028,10 +18124,10 @@
     </row>
     <row r="36" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="38" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C36" s="36">
         <f>MIN('Budget 36 mois'!E80:AN80)</f>
@@ -18047,7 +18143,7 @@
     </row>
     <row r="37" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B37"/>
       <c r="C37" s="70">
@@ -18064,10 +18160,10 @@
     </row>
     <row r="38" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C38" s="64">
         <f>'Budget 36 mois'!P80</f>
@@ -18075,11 +18171,11 @@
       </c>
       <c r="D38" s="64">
         <f>'Budget 36 mois'!AB80</f>
-        <v>496353.49647619051</v>
+        <v>500793.49647619051</v>
       </c>
       <c r="E38" s="64">
         <f>'Budget 36 mois'!AN80</f>
-        <v>871460.35847619059</v>
+        <v>875860.35847619059</v>
       </c>
       <c r="F38"/>
       <c r="G38"/>
@@ -18089,10 +18185,10 @@
     </row>
     <row r="39" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C39" s="64">
         <f>'Budget 36 mois'!B73</f>
@@ -18126,7 +18222,7 @@
     </row>
     <row r="41" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="60" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
@@ -18385,45 +18481,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="59" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C4" s="61">
         <v>0.45</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="C5" s="74">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="C6" s="74">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -18431,22 +18527,22 @@
         <v>26</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="C7" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="62" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" s="62" t="s">
+        <v>361</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="62" t="s">
         <v>139</v>
-      </c>
-      <c r="D7" s="62" t="s">
-        <v>367</v>
-      </c>
-      <c r="E7" s="62" t="s">
-        <v>368</v>
-      </c>
-      <c r="F7" s="62" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="62" t="s">
-        <v>141</v>
       </c>
       <c r="H7" s="62" t="s">
         <v>32</v>
@@ -18457,7 +18553,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="34" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B8" s="34">
         <v>2</v>
@@ -18484,12 +18580,12 @@
         <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="34" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B9" s="76">
         <f>MAX('Budget 36 mois'!E20:AN20)</f>
@@ -18517,12 +18613,12 @@
         <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B10" s="76">
         <f>MAX('Budget 36 mois'!E21:AN21)</f>
@@ -18550,12 +18646,12 @@
         <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="34" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B11" s="34">
         <v>1</v>
@@ -18582,12 +18678,12 @@
         <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B12" s="38">
         <f>SUM(B8:B11)</f>
@@ -18610,7 +18706,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="60" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/2 FINANCE/PREVISIONS/2026 1028 Modèle Pop Tables - Budget sur 36 mois, plan financier, prix et marges.xlsx
+++ b/2 FINANCE/PREVISIONS/2026 1028 Modèle Pop Tables - Budget sur 36 mois, plan financier, prix et marges.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\PREVISIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032AA5BA-CFB8-4D80-9C66-00DDF09E1545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B348408B-D66C-4A10-8114-4E7546F0519F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{09426CC5-4BCC-48B7-8854-C5C8E2CE30D1}"/>
   </bookViews>
@@ -493,9 +493,6 @@
     <t>Fondateurs (rémunération)</t>
   </si>
   <si>
-    <t>H : deux fondateurs rémunérés à partir de l'année 3 ; montant à décider par la Direction</t>
-  </si>
-  <si>
     <t>Coordinateur ou coordinatrice d'événements</t>
   </si>
   <si>
@@ -1072,9 +1069,6 @@
     <t>Flux de trésorerie du mois</t>
   </si>
   <si>
-    <t>Résultat - investissements + effet de la TVA + effet de la pré-vente + apport. Sans prêt, subvention ni levée</t>
-  </si>
-  <si>
     <t>Trésorerie en fin de mois (avant levée)</t>
   </si>
   <si>
@@ -1441,12 +1435,6 @@
     <t>Repérage, déplacements, communication locale, recrutement des extras, conseils locaux : coût par ville en France (B86) ou à l'étranger (B87), réparti sur les 3 mois qui précèdent la première soirée (dates C97:C101). Calculé automatiquement</t>
   </si>
   <si>
-    <t>Apport initial (love money, D-26)</t>
-  </si>
-  <si>
-    <t>Décision D-26 (29/10/2026, matin) : mise de fonds initiale de 70 000 € en love money (apport des proches), en novembre 2026. Forme (capital, compte courant, BSA AIR) à définir par le Juridique ; aucun fonds versé</t>
-  </si>
-  <si>
     <t>Ville (D-15, D-25)</t>
   </si>
   <si>
@@ -1474,9 +1462,6 @@
     <t>D-21 : 40 par ville active et par an dès l'année 2 ; volume à confirmer par les Ventes (D-16)</t>
   </si>
   <si>
-    <t>Trésorerie : point bas sur 36 mois (apport de 70 000 € en love money D-26, TVA et pré-vente compris, avant levée)</t>
-  </si>
-  <si>
     <t>Décisions de la Direction : D-05 (28/10/2026, « Jauge - validé suivant fichier finance ») pour les places à l'unité, 40 / 35 / 30 couverts ; D-22 (28/10/2026, soir) pour la privatisation, 30 couverts</t>
   </si>
   <si>
@@ -1489,7 +1474,22 @@
     <t>Pop Tables · Pôle Finance · Version du 29/10/2026, selon les décisions D-02 à D-26. Remplace le modèle du 27/10 (rangé dans 2 FINANCE/OLD).</t>
   </si>
   <si>
-    <t>Budget revu par le responsable Finance le 28/10/2026 (soir), devenu référence décidée (D-21, D-22). Mis à jour le 29/10/2026 : villes 2 et 3 en France dès novembre 2027, villes 4 à 6 à l'étranger dès novembre 2028 (D-25) ; apport initial de 70 000 € en love money (D-26). Lignes 14 à 17 calculées à partir du calendrier des villes. Toutes les autres valeurs restent des hypothèses (H) : voir la fiche des données manquantes.</t>
+    <t>Capital initial (7 fondateurs à parts égales)</t>
+  </si>
+  <si>
+    <t>Capital initial de 70 000 €, apporté à parts égales par les 7 fondateurs (10 000 € chacun) à la création de la SAS, en novembre 2026. Choix du responsable Finance (29/10/2026), qui précise la forme de la mise de fonds de D-26 ; pas de BSA AIR. Aucun fonds versé</t>
+  </si>
+  <si>
+    <t>Résultat - investissements + effet de la TVA + effet de la pré-vente + capital initial. Sans prêt, subvention ni levée</t>
+  </si>
+  <si>
+    <t>H : les deux fondateurs exécutifs (choix du responsable Finance, 29/10/2026), rémunérés à partir de l'année 3 ; montant à décider par la Direction. Les 5 autres fondateurs sont associés sans rémunération</t>
+  </si>
+  <si>
+    <t>Trésorerie : point bas sur 36 mois (capital initial de 70 000 €, TVA et pré-vente compris, avant levée)</t>
+  </si>
+  <si>
+    <t>Budget revu par le responsable Finance le 28/10/2026 (soir), devenu référence décidée (D-21, D-22). Mis à jour le 29/10/2026 : villes 2 et 3 en France dès novembre 2027, villes 4 à 6 à l'étranger dès novembre 2028 (D-25) ; capital initial de 70 000 € apporté à parts égales par les 7 fondateurs (SAS, D-26 précisée par le responsable Finance), dont 2 fondateurs exécutifs. Lignes 14 à 17 calculées à partir du calendrier des villes. Toutes les autres valeurs restent des hypothèses (H) : voir la fiche des données manquantes.</t>
   </si>
 </sst>
 </file>
@@ -1854,8 +1854,8 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2239,12 +2239,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13" x14ac:dyDescent="0.25">
@@ -2276,7 +2276,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="25" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="25" x14ac:dyDescent="0.25">
@@ -2353,34 +2353,34 @@
     </row>
     <row r="17" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="50" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="50" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2483,10 +2483,10 @@
         <v>115</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -2512,7 +2512,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>83</v>
@@ -2568,7 +2568,7 @@
         <v>80</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>81</v>
@@ -2595,7 +2595,7 @@
         <v>80</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="I11" s="20" t="s">
         <v>81</v>
@@ -2983,7 +2983,7 @@
     </row>
     <row r="26" spans="1:9" ht="50" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>51</v>
@@ -3008,10 +3008,10 @@
         <v>115</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -3188,7 +3188,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>51</v>
@@ -3209,10 +3209,10 @@
         <v>115</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="13" x14ac:dyDescent="0.25">
@@ -3501,17 +3501,17 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="38" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D4" s="45"/>
       <c r="E4" s="45"/>
@@ -3521,18 +3521,18 @@
         <v>80</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>102</v>
@@ -3544,18 +3544,18 @@
         <v>104</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="42">
         <v>9</v>
@@ -3579,12 +3579,12 @@
         <v>0</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" s="42">
         <v>8</v>
@@ -3608,12 +3608,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B9" s="42">
         <v>7</v>
@@ -3637,12 +3637,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B10" s="42">
         <v>7</v>
@@ -3666,12 +3666,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="42">
         <v>7</v>
@@ -3695,12 +3695,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B12" s="42">
         <v>7</v>
@@ -3724,12 +3724,12 @@
         <v>0</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="42">
         <v>7</v>
@@ -3753,12 +3753,12 @@
         <v>0</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B14" s="42">
         <v>10</v>
@@ -3782,12 +3782,12 @@
         <v>0</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B15" s="42">
         <v>5</v>
@@ -3811,17 +3811,17 @@
         <v>0</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="19" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="20" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="21" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
@@ -3913,18 +3913,18 @@
     </row>
     <row r="23" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>102</v>
@@ -3936,13 +3936,13 @@
         <v>104</v>
       </c>
       <c r="G25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -4041,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -4074,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -4107,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="25" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -4239,12 +4239,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4267,7 +4267,7 @@
     </row>
     <row r="37" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="38" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4313,7 +4313,7 @@
     </row>
     <row r="39" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B39" s="39"/>
       <c r="C39" s="39"/>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="40" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4359,12 +4359,12 @@
     </row>
     <row r="42" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -4388,17 +4388,17 @@
   <sheetData>
     <row r="1" spans="1:43" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B3" s="53">
         <v>46327</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="D4" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E4" s="54">
         <v>1</v>
@@ -4522,13 +4522,13 @@
         <v>26</v>
       </c>
       <c r="B5" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="58" t="s">
         <v>268</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="D5" s="58" t="s">
         <v>269</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>270</v>
       </c>
       <c r="E5" s="51">
         <f t="shared" ref="E5:AN5" si="0">EDATE($B$3,E$4-1)</f>
@@ -4678,15 +4678,15 @@
         <v>32</v>
       </c>
       <c r="AP5" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AQ5" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="7" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B7" s="13">
         <f>P7</f>
@@ -4856,15 +4856,15 @@
         <v>6</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B8" s="13">
         <f t="shared" ref="B8:B19" si="1">SUM(E8:P8)</f>
@@ -4990,12 +4990,12 @@
         <v>82</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B9" s="13">
         <f t="shared" si="1"/>
@@ -5121,12 +5121,12 @@
         <v>82</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B10" s="13">
         <f t="shared" si="1"/>
@@ -5252,12 +5252,12 @@
         <v>82</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B11" s="13">
         <f t="shared" si="1"/>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="12" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B12" s="13">
         <f t="shared" si="1"/>
@@ -5568,7 +5568,7 @@
         <v>82</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:43" ht="13" x14ac:dyDescent="0.3">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="14" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B14" s="13">
         <f t="shared" si="1"/>
@@ -5896,12 +5896,12 @@
         <v>115</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B15" s="13">
         <f t="shared" si="1"/>
@@ -6063,12 +6063,12 @@
         <v>115</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B16" s="13">
         <f>SUM(E16:P16)</f>
@@ -6230,12 +6230,12 @@
         <v>115</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B17" s="13">
         <f>SUM(E17:P17)</f>
@@ -6397,12 +6397,12 @@
         <v>115</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B18" s="13">
         <f t="shared" si="1"/>
@@ -6528,12 +6528,12 @@
         <v>80</v>
       </c>
       <c r="AP18" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B19" s="13">
         <f t="shared" si="1"/>
@@ -6659,12 +6659,12 @@
         <v>80</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B20" s="13">
         <f>MAX(E20:P20)</f>
@@ -6826,12 +6826,12 @@
         <v>115</v>
       </c>
       <c r="AP20" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B21" s="13">
         <f>MAX(E21:P21)</f>
@@ -6993,12 +6993,12 @@
         <v>115</v>
       </c>
       <c r="AP21" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B22" s="13">
         <f>MAX(E22:P22)</f>
@@ -7160,12 +7160,12 @@
         <v>115</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="24" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B24" s="16">
         <f t="shared" ref="B24:B31" si="11">SUM(E24:P24)</f>
@@ -7371,12 +7371,12 @@
         <v>83928.57142857142</v>
       </c>
       <c r="AP24" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" s="16">
         <f t="shared" si="11"/>
@@ -7698,7 +7698,7 @@
     </row>
     <row r="27" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B27" s="16">
         <f t="shared" si="11"/>
@@ -7857,12 +7857,12 @@
         <v>244364.99999999997</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" s="16">
         <f t="shared" si="11"/>
@@ -8024,12 +8024,12 @@
         <v>82</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" s="16">
         <f t="shared" si="11"/>
@@ -8191,7 +8191,7 @@
         <v>82</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AQ29" s="55">
         <v>0.1</v>
@@ -8523,7 +8523,7 @@
     </row>
     <row r="32" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -8733,7 +8733,7 @@
         <v>82</v>
       </c>
       <c r="AP33" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AQ33" s="55"/>
     </row>
@@ -8902,7 +8902,7 @@
         <v>115</v>
       </c>
       <c r="AP34" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AQ34" s="55"/>
     </row>
@@ -9071,7 +9071,7 @@
         <v>115</v>
       </c>
       <c r="AP35" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AQ35" s="55"/>
     </row>
@@ -9240,7 +9240,7 @@
         <v>82</v>
       </c>
       <c r="AP36" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AQ36" s="55"/>
     </row>
@@ -9408,7 +9408,7 @@
     </row>
     <row r="38" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -9617,7 +9617,7 @@
         <v>115</v>
       </c>
       <c r="AP39" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AQ39" s="57">
         <f>TVA!$C$30</f>
@@ -9626,7 +9626,7 @@
     </row>
     <row r="40" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="16">
         <f t="shared" si="19"/>
@@ -9788,7 +9788,7 @@
         <v>115</v>
       </c>
       <c r="AP40" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AQ40" s="57">
         <f>TVA!$C$31</f>
@@ -9797,7 +9797,7 @@
     </row>
     <row r="41" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B41" s="16">
         <f t="shared" si="19"/>
@@ -9923,7 +9923,7 @@
         <v>82</v>
       </c>
       <c r="AP41" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AQ41" s="57">
         <f>TVA!$C$32</f>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="42" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B42" s="16">
         <f t="shared" si="19"/>
@@ -10058,7 +10058,7 @@
         <v>82</v>
       </c>
       <c r="AP42" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AQ42" s="57">
         <v>0.2</v>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="43" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B43" s="16">
         <f t="shared" si="19"/>
@@ -10192,7 +10192,7 @@
         <v>82</v>
       </c>
       <c r="AP43" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AQ43" s="57">
         <v>0.1</v>
@@ -10200,7 +10200,7 @@
     </row>
     <row r="44" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B44" s="16">
         <f t="shared" si="19"/>
@@ -10326,7 +10326,7 @@
         <v>82</v>
       </c>
       <c r="AP44" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AQ44" s="57">
         <v>0.2</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="45" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B45" s="16">
         <f t="shared" si="19"/>
@@ -10460,7 +10460,7 @@
         <v>82</v>
       </c>
       <c r="AP45" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AQ45" s="57">
         <v>0.1</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="46" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B46" s="16">
         <f t="shared" si="19"/>
@@ -10630,7 +10630,7 @@
         <v>82</v>
       </c>
       <c r="AP46" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AQ46" s="57">
         <v>0.1</v>
@@ -10638,7 +10638,7 @@
     </row>
     <row r="47" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B47" s="16">
         <f t="shared" si="19"/>
@@ -10764,7 +10764,7 @@
         <v>82</v>
       </c>
       <c r="AP47" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AQ47" s="57">
         <v>0.2</v>
@@ -10772,7 +10772,7 @@
     </row>
     <row r="48" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B48" s="16">
         <f t="shared" si="19"/>
@@ -10934,7 +10934,7 @@
         <v>82</v>
       </c>
       <c r="AP48" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AQ48" s="57">
         <f>TVA!$C$33</f>
@@ -11069,7 +11069,7 @@
         <v>82</v>
       </c>
       <c r="AP49" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AQ49" s="57">
         <f>TVA!$C$34</f>
@@ -11204,7 +11204,7 @@
         <v>82</v>
       </c>
       <c r="AP50" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AQ50" s="57">
         <f>TVA!$C$35</f>
@@ -11213,7 +11213,7 @@
     </row>
     <row r="51" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B51" s="16">
         <f t="shared" si="19"/>
@@ -11339,7 +11339,7 @@
         <v>82</v>
       </c>
       <c r="AP51" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AQ51" s="57">
         <f>TVA!$C$36</f>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="52" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B52" s="16">
         <f t="shared" si="19"/>
@@ -11510,7 +11510,7 @@
         <v>115</v>
       </c>
       <c r="AP52" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AQ52" s="57">
         <v>0.1</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="53" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B53" s="16">
         <f t="shared" si="19"/>
@@ -11644,7 +11644,7 @@
         <v>82</v>
       </c>
       <c r="AP53" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AQ53" s="57">
         <v>0</v>
@@ -11652,7 +11652,7 @@
     </row>
     <row r="54" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B54" s="16">
         <f t="shared" si="19"/>
@@ -11778,7 +11778,7 @@
         <v>82</v>
       </c>
       <c r="AP54" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AQ54" s="57">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>82</v>
       </c>
       <c r="AP55" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AQ55" s="57">
         <f>TVA!$C$37</f>
@@ -11921,7 +11921,7 @@
     </row>
     <row r="56" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B56" s="16">
         <f t="shared" si="19"/>
@@ -12245,7 +12245,7 @@
     </row>
     <row r="58" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -12616,7 +12616,7 @@
     </row>
     <row r="61" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -12663,7 +12663,7 @@
     </row>
     <row r="62" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B62" s="16">
         <f>SUM(E62:P62)</f>
@@ -12789,7 +12789,7 @@
         <v>115</v>
       </c>
       <c r="AP62" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AQ62" s="55">
         <f>TVA!$C$38</f>
@@ -12798,7 +12798,7 @@
     </row>
     <row r="63" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B63" s="16">
         <f>SUM(E63:P63)</f>
@@ -12924,7 +12924,7 @@
         <v>82</v>
       </c>
       <c r="AP63" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AQ63" s="55">
         <f>TVA!$C$38</f>
@@ -12933,7 +12933,7 @@
     </row>
     <row r="64" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B64" s="16">
         <f>SUM(E64:P64)</f>
@@ -13095,7 +13095,7 @@
     </row>
     <row r="65" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="66" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B66" s="16">
         <f>SUM(E66:P66)</f>
@@ -13304,7 +13304,7 @@
     </row>
     <row r="67" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B67" s="16">
         <f>SUM(E67:P67)</f>
@@ -13466,7 +13466,7 @@
     </row>
     <row r="68" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B68" s="16">
         <f>SUM(E68:P68)</f>
@@ -13628,7 +13628,7 @@
     </row>
     <row r="69" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B69" s="16">
         <f>SUM(E69:P69)</f>
@@ -13790,7 +13790,7 @@
     </row>
     <row r="70" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B70" s="16">
         <f>SUM(E70:P70)</f>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E71" s="15">
         <v>0</v>
@@ -14099,7 +14099,7 @@
     </row>
     <row r="72" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B72" s="16">
         <f>SUM(E72:P72)</f>
@@ -14260,7 +14260,7 @@
     </row>
     <row r="73" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B73" s="16">
         <f>P73</f>
@@ -14421,7 +14421,7 @@
     </row>
     <row r="74" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B74" s="16">
         <f>SUM(E74:P74)</f>
@@ -14581,7 +14581,7 @@
     </row>
     <row r="75" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B75" s="16">
         <f>SUM(E75:P75)</f>
@@ -14742,7 +14742,7 @@
     </row>
     <row r="76" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
@@ -14789,7 +14789,7 @@
     </row>
     <row r="77" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B77" s="16">
         <f>SUM(E77:P77)</f>
@@ -14950,12 +14950,12 @@
         <v>82</v>
       </c>
       <c r="AP77" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="78" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B78" s="16">
         <f>SUM(E78:P78)</f>
@@ -15081,12 +15081,12 @@
         <v>82</v>
       </c>
       <c r="AP78" s="1" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B79" s="16">
         <f>SUM(E79:P79)</f>
@@ -15245,12 +15245,12 @@
         <v>32725.259333333335</v>
       </c>
       <c r="AP79" s="1" t="s">
-        <v>334</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B80" s="16">
         <f>P80</f>
@@ -15411,7 +15411,7 @@
     </row>
     <row r="82" spans="1:43" ht="13" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
@@ -15458,235 +15458,235 @@
     </row>
     <row r="83" spans="1:43" ht="26" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B84" s="14">
         <v>300</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B85" s="14">
         <v>700</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B86" s="14">
         <v>15000</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B87" s="14">
         <v>15000</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B88" s="11">
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B89" s="41">
         <v>0.02</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B90" s="71">
         <v>40</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B91" s="71">
         <v>300</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B92" s="71">
         <v>80</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B93" s="71">
         <v>50</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="95" spans="1:43" ht="26" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C96" s="52">
         <f>EDATE($B$3,2)</f>
         <v>46388</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C97" s="52">
         <f>EDATE($B$3,12)</f>
         <v>46692</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C98" s="52">
         <f>EDATE($B$3,12)</f>
         <v>46692</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C99" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C100" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C101" s="52">
         <f>EDATE($B$3,24)</f>
         <v>47058</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -15708,91 +15708,91 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="26" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" s="1">
         <v>19</v>
@@ -15804,12 +15804,12 @@
         <v>82</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="1">
         <v>22</v>
@@ -15821,15 +15821,15 @@
         <v>82</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C12" s="41">
         <v>5.5E-2</v>
@@ -15838,15 +15838,15 @@
         <v>82</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="C13" s="41">
         <v>0.2</v>
@@ -15855,15 +15855,15 @@
         <v>82</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C14" s="41">
         <v>0.2</v>
@@ -15872,12 +15872,12 @@
         <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" s="1">
         <v>27</v>
@@ -15906,12 +15906,12 @@
         <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="1">
         <v>29</v>
@@ -15931,7 +15931,7 @@
         <v>67</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C18" s="41">
         <v>0</v>
@@ -15940,15 +15940,15 @@
         <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="C19" s="41">
         <v>0.2</v>
@@ -15962,7 +15962,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B20" s="1">
         <v>33</v>
@@ -15974,12 +15974,12 @@
         <v>82</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="26" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
@@ -15992,12 +15992,12 @@
         <v>104</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="15">
         <f>'Prix et marges'!C17</f>
@@ -16018,7 +16018,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C24" s="50">
         <f>'Prix et marges'!C12</f>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C25" s="15">
         <f>C23*C24</f>
@@ -16060,7 +16060,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C26" s="15">
         <f>'Prix et marges'!C19*$C$10+'Prix et marges'!C22*$C$11+'Prix et marges'!C9*'Prix et marges'!C23*$C$12+'Prix et marges'!C9*'Prix et marges'!C24*$C$13+'Prix et marges'!C26*$C$14+'Prix et marges'!C27*$C$15+'Prix et marges'!C28*$C$16+'Prix et marges'!C29*$C$17+'Prix et marges'!C30*'Prix et marges'!C17*$C$18+'Prix et marges'!C31*'Prix et marges'!C17*$C$19+'Prix et marges'!C33*$C$20</f>
@@ -16081,7 +16081,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C27" s="15">
         <f>C25-C26</f>
@@ -16102,27 +16102,27 @@
     </row>
     <row r="29" spans="1:6" ht="26" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>246</v>
-      </c>
       <c r="C29" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C30" s="41">
         <v>0.2</v>
@@ -16136,10 +16136,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C31" s="41">
         <v>0.2</v>
@@ -16156,7 +16156,7 @@
         <v>108</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C32" s="41">
         <v>0.2</v>
@@ -16165,15 +16165,15 @@
         <v>82</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C33" s="41">
         <v>0</v>
@@ -16182,15 +16182,15 @@
         <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C34" s="41">
         <v>0.2</v>
@@ -16207,7 +16207,7 @@
         <v>110</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C35" s="41">
         <v>0</v>
@@ -16216,7 +16216,7 @@
         <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -16224,7 +16224,7 @@
         <v>111</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C36" s="41">
         <v>0.1</v>
@@ -16233,7 +16233,7 @@
         <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -16241,7 +16241,7 @@
         <v>112</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C37" s="41">
         <v>0</v>
@@ -16250,15 +16250,15 @@
         <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C38" s="41">
         <v>0.2</v>
@@ -16272,7 +16272,7 @@
     </row>
     <row r="40" spans="1:14" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="60" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B40"/>
       <c r="C40"/>
@@ -16626,12 +16626,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -17355,7 +17355,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="59" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -17369,7 +17369,7 @@
     </row>
     <row r="2" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -17422,7 +17422,7 @@
         <v>126</v>
       </c>
       <c r="F5" s="62" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -17445,10 +17445,10 @@
     </row>
     <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C7" s="66">
         <f>'Budget 36 mois'!B7</f>
@@ -17463,7 +17463,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C8" s="66">
         <f>'Budget 36 mois'!B11</f>
@@ -17490,7 +17490,7 @@
         <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -17499,10 +17499,10 @@
     </row>
     <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C9" s="66">
         <f>'Budget 36 mois'!B8</f>
@@ -17524,10 +17524,10 @@
     </row>
     <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C10" s="66">
         <f>'Budget 36 mois'!B9</f>
@@ -17549,10 +17549,10 @@
     </row>
     <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B11" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C11" s="66">
         <f>'Budget 36 mois'!B10</f>
@@ -17574,10 +17574,10 @@
     </row>
     <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C12" s="66">
         <f>'Budget 36 mois'!B12</f>
@@ -17592,7 +17592,7 @@
         <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
@@ -17604,7 +17604,7 @@
         <v>105</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C13" s="69">
         <f>'Budget 36 mois'!B13</f>
@@ -17665,7 +17665,7 @@
     </row>
     <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
@@ -17730,7 +17730,7 @@
     </row>
     <row r="19" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
@@ -17748,7 +17748,7 @@
         <v>643836.88800000015</v>
       </c>
       <c r="F19" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -17757,7 +17757,7 @@
     </row>
     <row r="20" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
@@ -17782,7 +17782,7 @@
     </row>
     <row r="21" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B21" t="s">
         <v>51</v>
@@ -17800,7 +17800,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -17809,7 +17809,7 @@
     </row>
     <row r="22" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B22" t="s">
         <v>51</v>
@@ -17827,7 +17827,7 @@
         <v>29210.000000000004</v>
       </c>
       <c r="F22" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -17836,7 +17836,7 @@
     </row>
     <row r="23" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
@@ -17861,7 +17861,7 @@
     </row>
     <row r="24" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
@@ -17886,7 +17886,7 @@
     </row>
     <row r="25" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
@@ -17904,7 +17904,7 @@
         <v>76559.999999999971</v>
       </c>
       <c r="F25" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
@@ -17963,7 +17963,7 @@
     </row>
     <row r="28" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="37" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
@@ -17977,7 +17977,7 @@
     </row>
     <row r="29" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
@@ -18002,7 +18002,7 @@
     </row>
     <row r="30" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B30" t="s">
         <v>130</v>
@@ -18070,7 +18070,7 @@
         <v>212.59935743716258</v>
       </c>
       <c r="F32" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
@@ -18091,7 +18091,7 @@
     </row>
     <row r="34" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="37" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="37"/>
@@ -18105,7 +18105,7 @@
     </row>
     <row r="35" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="38" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B35" s="38" t="s">
         <v>130</v>
@@ -18124,7 +18124,7 @@
     </row>
     <row r="36" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="38" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B36" s="38" t="s">
         <v>130</v>
@@ -18143,7 +18143,7 @@
     </row>
     <row r="37" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B37"/>
       <c r="C37" s="70">
@@ -18160,7 +18160,7 @@
     </row>
     <row r="38" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B38" t="s">
         <v>130</v>
@@ -18185,7 +18185,7 @@
     </row>
     <row r="39" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s">
         <v>130</v>
@@ -18222,7 +18222,7 @@
     </row>
     <row r="41" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="60" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B41"/>
       <c r="C41"/>
@@ -18481,12 +18481,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="59" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -18502,24 +18502,24 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C5" s="74">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C6" s="74">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -18527,16 +18527,16 @@
         <v>26</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C7" s="62" t="s">
         <v>137</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F7" s="62" t="s">
         <v>138</v>
@@ -18580,12 +18580,12 @@
         <v>82</v>
       </c>
       <c r="I8" t="s">
-        <v>141</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" s="76">
         <f>MAX('Budget 36 mois'!E20:AN20)</f>
@@ -18613,12 +18613,12 @@
         <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="76">
         <f>MAX('Budget 36 mois'!E21:AN21)</f>
@@ -18646,12 +18646,12 @@
         <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="34" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B11" s="34">
         <v>1</v>
@@ -18678,7 +18678,7 @@
         <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -18706,7 +18706,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="60" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
